--- a/jogos_2025-07-27.xlsx
+++ b/jogos_2025-07-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="359">
   <si>
     <t>Date</t>
   </si>
@@ -247,39 +247,39 @@
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>Japan J1 League</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
-    <t>Japan J1 League</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
+    <t>Sweden Superettan</t>
   </si>
   <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>China China League One</t>
   </si>
   <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Russia Russian Premier League</t>
   </si>
   <si>
@@ -292,33 +292,33 @@
     <t>Czech Republic First League</t>
   </si>
   <si>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
     <t>Hungary NB I</t>
   </si>
   <si>
+    <t>Chile Primera División</t>
+  </si>
+  <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Slovakia Super Liga</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
-    <t>Chile Primera División</t>
+    <t>Hungary NB II</t>
   </si>
   <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Hungary NB II</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
@@ -349,96 +349,96 @@
     <t>San Jose Earthquakes II</t>
   </si>
   <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
+    <t>Central Coast II</t>
+  </si>
+  <si>
     <t>Rockdale City Suns</t>
   </si>
   <si>
-    <t>Central Coast II</t>
-  </si>
-  <si>
-    <t>St. George Saints</t>
+    <t>Viktoria Žižkov</t>
   </si>
   <si>
     <t>Slavia Praha II</t>
   </si>
   <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
     <t>Yenisey</t>
   </si>
   <si>
+    <t>Urawa Reds</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
     <t>Incheon United</t>
   </si>
   <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
-    <t>Urawa Reds</t>
-  </si>
-  <si>
-    <t>Wieczysta Kraków</t>
+    <t>Daegu</t>
   </si>
   <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Daegu</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
     <t>Seongnam</t>
   </si>
   <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
-    <t>Kalmar</t>
-  </si>
-  <si>
     <t>Qingdao Jonoon</t>
   </si>
   <si>
     <t>Dalian Huayi</t>
   </si>
   <si>
+    <t>Nantong Zhiyun</t>
+  </si>
+  <si>
+    <t>RSC Anderlecht</t>
+  </si>
+  <si>
+    <t>Guangzhou E-Power</t>
+  </si>
+  <si>
     <t>Guangxi Baoyun</t>
   </si>
   <si>
-    <t>Nantong Zhiyun</t>
-  </si>
-  <si>
-    <t>Guangzhou E-Power</t>
-  </si>
-  <si>
-    <t>RSC Anderlecht</t>
-  </si>
-  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
+    <t>Häcken</t>
+  </si>
+  <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
+    <t>OB</t>
+  </si>
+  <si>
     <t>Vaduz</t>
   </si>
   <si>
+    <t>CSKA Moskva</t>
+  </si>
+  <si>
     <t>AIK</t>
   </si>
   <si>
-    <t>Häcken</t>
-  </si>
-  <si>
-    <t>OB</t>
-  </si>
-  <si>
-    <t>Shandong Luneng</t>
-  </si>
-  <si>
-    <t>CSKA Moskva</t>
-  </si>
-  <si>
     <t>Rosenborg</t>
   </si>
   <si>
@@ -454,235 +454,241 @@
     <t>Falkenberg</t>
   </si>
   <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
     <t>Örgryte</t>
   </si>
   <si>
-    <t>Slovan Liberec</t>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
+    <t>Lugano</t>
   </si>
   <si>
     <t>Inter Turku</t>
   </si>
   <si>
-    <t>Lugano</t>
-  </si>
-  <si>
     <t>Vestri</t>
   </si>
   <si>
+    <t>Neftekhimik</t>
+  </si>
+  <si>
+    <t>Nyíregyháza Spartacus</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
     <t>OH Leuven</t>
   </si>
   <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>Nyíregyháza Spartacus</t>
-  </si>
-  <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
-    <t>Neftekhimik</t>
+    <t>Orenburg</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
   </si>
   <si>
     <t>Värnamo</t>
   </si>
   <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>Orenburg</t>
+    <t>Universidad Católica</t>
+  </si>
+  <si>
+    <t>Krasnodar</t>
+  </si>
+  <si>
+    <t>Turan Turkistan</t>
   </si>
   <si>
     <t>Rodina Moskva</t>
   </si>
   <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Podbrezová</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
+    <t>Videoton</t>
+  </si>
+  <si>
     <t>Skalica</t>
   </si>
   <si>
-    <t>Podbrezová</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Turan Turkistan</t>
-  </si>
-  <si>
-    <t>Universidad Católica</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Krasnodar</t>
+    <t>Mezőkövesd-Zsóry</t>
+  </si>
+  <si>
+    <t>Jagiellonia Białystok</t>
   </si>
   <si>
     <t>CFR Cluj</t>
   </si>
   <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>Jagiellonia Białystok</t>
+    <t>Fakel</t>
+  </si>
+  <si>
+    <t>Arda</t>
+  </si>
+  <si>
+    <t>Nordsjælland</t>
   </si>
   <si>
     <t>Paksi SE</t>
   </si>
   <si>
-    <t>Arda</t>
-  </si>
-  <si>
-    <t>Nordsjælland</t>
-  </si>
-  <si>
-    <t>Fakel</t>
+    <t>O'Higgins</t>
   </si>
   <si>
     <t>Club Brugge</t>
   </si>
   <si>
-    <t>O'Higgins</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>Kozármisleny</t>
+  </si>
+  <si>
+    <t>Budafoki MTE</t>
+  </si>
+  <si>
+    <t>BVSC</t>
+  </si>
+  <si>
+    <t>Vasas</t>
+  </si>
+  <si>
+    <t>Szeged 2011</t>
+  </si>
+  <si>
     <t>Rubin Kazan</t>
   </si>
   <si>
-    <t>Vasas</t>
-  </si>
-  <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
     <t>Napredak</t>
   </si>
   <si>
+    <t>Spartak Trnava</t>
+  </si>
+  <si>
     <t>Soroksár SC</t>
   </si>
   <si>
-    <t>Spartak Trnava</t>
-  </si>
-  <si>
-    <t>BVSC</t>
-  </si>
-  <si>
-    <t>Kozármisleny</t>
-  </si>
-  <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
     <t>Radnički Kragujevac</t>
   </si>
   <si>
-    <t>IMT Novi Beograd</t>
+    <t>Alvarado</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Puskás</t>
+  </si>
+  <si>
+    <t>Arsenal de Sarandí</t>
+  </si>
+  <si>
+    <t>Chicago Fire II</t>
   </si>
   <si>
     <t>Sparta Praha</t>
   </si>
   <si>
-    <t>Arsenal de Sarandí</t>
-  </si>
-  <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Puskás</t>
-  </si>
-  <si>
     <t>Celje</t>
   </si>
   <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
-    <t>Korona Kielce</t>
+    <t>Colegiales</t>
+  </si>
+  <si>
+    <t>Defensores Unidos</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
   </si>
   <si>
     <t>Temperley</t>
   </si>
   <si>
-    <t>Colegiales</t>
-  </si>
-  <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
     <t>Colón</t>
   </si>
   <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Estudiantes Río Cuarto</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
     <t>Coritiba</t>
   </si>
   <si>
-    <t>Volta Redonda</t>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
   </si>
   <si>
     <t>Palestino</t>
   </si>
   <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Estudiantes Río Cuarto</t>
+    <t>KA</t>
   </si>
   <si>
     <t>Valur</t>
   </si>
   <si>
+    <t>KR</t>
+  </si>
+  <si>
     <t>Fram</t>
   </si>
   <si>
-    <t>KA</t>
-  </si>
-  <si>
-    <t>KR</t>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Chaco For Ever</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
   </si>
   <si>
     <t>Figueirense</t>
   </si>
   <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Chaco For Ever</t>
-  </si>
-  <si>
     <t>Gimnasia y Tiro</t>
   </si>
   <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
     <t>Internacional</t>
   </si>
   <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>América Mineiro</t>
+    <t>São Bernardo</t>
   </si>
   <si>
     <t>Columbus Crew II</t>
@@ -691,9 +697,6 @@
     <t>Atlético GO</t>
   </si>
   <si>
-    <t>São Bernardo</t>
-  </si>
-  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
@@ -715,96 +718,96 @@
     <t>Real Monarchs</t>
   </si>
   <si>
+    <t>Blacktown City</t>
+  </si>
+  <si>
+    <t>Sydney II</t>
+  </si>
+  <si>
     <t>Sydney United</t>
   </si>
   <si>
-    <t>Sydney II</t>
-  </si>
-  <si>
-    <t>Blacktown City</t>
+    <t>Vyškov</t>
   </si>
   <si>
     <t>Líšeň</t>
   </si>
   <si>
-    <t>Vyškov</t>
-  </si>
-  <si>
     <t>SKA Khabarovsk</t>
   </si>
   <si>
+    <t>Avispa Fukuoka</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
     <t>Ansan Greeners</t>
   </si>
   <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Avispa Fukuoka</t>
-  </si>
-  <si>
-    <t>Pogoń Siedlce</t>
+    <t>Pohang Steelers</t>
   </si>
   <si>
     <t>Ulsan</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
     <t>Jeonnam Dragons</t>
   </si>
   <si>
+    <t>Utsikten</t>
+  </si>
+  <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Utsikten</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Qingdao Red Lions</t>
   </si>
   <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
+    <t>KVC Westerlo</t>
+  </si>
+  <si>
+    <t>Heilongjiang Lava Spring</t>
+  </si>
+  <si>
     <t>Suzhou Dongwu</t>
   </si>
   <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
-    <t>KVC Westerlo</t>
-  </si>
-  <si>
     <t>Henan Jianye</t>
   </si>
   <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
+    <t>Akhmat Grozny</t>
+  </si>
+  <si>
     <t>Öster</t>
   </si>
   <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
-    <t>Akhmat Grozny</t>
-  </si>
-  <si>
     <t>Tromsø</t>
   </si>
   <si>
@@ -820,244 +823,247 @@
     <t>Landskrona</t>
   </si>
   <si>
+    <t>Pardubice</t>
+  </si>
+  <si>
     <t>Östersunds FK</t>
   </si>
   <si>
-    <t>Pardubice</t>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Thun</t>
   </si>
   <si>
     <t>SJK</t>
   </si>
   <si>
-    <t>Thun</t>
-  </si>
-  <si>
     <t>ÍBV</t>
   </si>
   <si>
+    <t>Torpedo Moskva</t>
+  </si>
+  <si>
+    <t>Várda SE</t>
+  </si>
+  <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
     <t>Sporting Charleroi</t>
   </si>
   <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
-    <t>Várda SE</t>
-  </si>
-  <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
-    <t>Torpedo Moskva</t>
+    <t>Makhachkala</t>
+  </si>
+  <si>
+    <t>Sirius</t>
   </si>
   <si>
     <t>Hammarby</t>
   </si>
   <si>
-    <t>Sirius</t>
-  </si>
-  <si>
-    <t>Makhachkala</t>
+    <t>Coquimbo Unido</t>
+  </si>
+  <si>
+    <t>Lokomotiv Moskva</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
   </si>
   <si>
     <t>Spartak Kostroma</t>
   </si>
   <si>
+    <t>Tychy 71</t>
+  </si>
+  <si>
+    <t>FK Košice</t>
+  </si>
+  <si>
+    <t>Teplice</t>
+  </si>
+  <si>
+    <t>Honvéd W</t>
+  </si>
+  <si>
     <t>Žilina</t>
   </si>
   <si>
-    <t>FK Košice</t>
-  </si>
-  <si>
-    <t>Tychy 71</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Coquimbo Unido</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Lokomotiv Moskva</t>
+    <t>Karcag SE</t>
+  </si>
+  <si>
+    <t>Widzew Łódź</t>
   </si>
   <si>
     <t>Argeș</t>
   </si>
   <si>
-    <t>Karcag SE</t>
-  </si>
-  <si>
-    <t>Widzew Łódź</t>
+    <t>Ufa</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Brøndby</t>
   </si>
   <si>
     <t>Győri ETO</t>
   </si>
   <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Brøndby</t>
-  </si>
-  <si>
-    <t>Ufa</t>
+    <t>Colo-Colo</t>
   </si>
   <si>
     <t>KRC Genk</t>
   </si>
   <si>
-    <t>Colo-Colo</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>Tiszakécske</t>
+  </si>
+  <si>
+    <t>Szentlőrinc SE</t>
+  </si>
+  <si>
+    <t>Ajka</t>
+  </si>
+  <si>
+    <t>Csákvári TK</t>
+  </si>
+  <si>
+    <t>Kecskeméti TE</t>
+  </si>
+  <si>
     <t>Zenit</t>
   </si>
   <si>
-    <t>Csákvári TK</t>
-  </si>
-  <si>
-    <t>Szentlőrinc SE</t>
-  </si>
-  <si>
     <t>Novi Pazar</t>
   </si>
   <si>
+    <t>Ružomberok</t>
+  </si>
+  <si>
     <t>Békéscsaba</t>
   </si>
   <si>
-    <t>Ružomberok</t>
-  </si>
-  <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>Kecskeméti TE</t>
-  </si>
-  <si>
     <t>KAA Gent</t>
   </si>
   <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
     <t>Železničar Pančevo</t>
   </si>
   <si>
-    <t>Čukarički</t>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>Kazincbarcika</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>New York RB II</t>
   </si>
   <si>
     <t>Mladá Boleslav</t>
   </si>
   <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>New York RB II</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>Kazincbarcika</t>
-  </si>
-  <si>
     <t>Radomlje</t>
   </si>
   <si>
+    <t>Legia Warszawa</t>
+  </si>
+  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
-    <t>Legia Warszawa</t>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
+    <t>Dinamo Bucureşti</t>
+  </si>
+  <si>
+    <t>Central Norte</t>
   </si>
   <si>
     <t>Gimnasia Jujuy</t>
   </si>
   <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>Dinamo Bucureşti</t>
-  </si>
-  <si>
-    <t>Central Norte</t>
-  </si>
-  <si>
     <t>Gimnasia Mendoza</t>
   </si>
   <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Ceará</t>
+  </si>
+  <si>
     <t>Amazonas</t>
   </si>
   <si>
-    <t>Vila Nova</t>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
   </si>
   <si>
     <t>Unión Española</t>
   </si>
   <si>
-    <t>Ceará</t>
-  </si>
-  <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
+    <t>ÍA</t>
   </si>
   <si>
     <t>FH</t>
   </si>
   <si>
+    <t>Breidablik</t>
+  </si>
+  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
-    <t>ÍA</t>
-  </si>
-  <si>
-    <t>Breidablik</t>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>Ituano</t>
   </si>
   <si>
     <t>Anápolis</t>
   </si>
   <si>
-    <t>Ponte Preta</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
     <t>San Martín Tucumán</t>
   </si>
   <si>
+    <t>Atlético PR</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
-    <t>Juventude</t>
-  </si>
-  <si>
-    <t>Atlético PR</t>
+    <t>Confiança</t>
   </si>
   <si>
     <t>Toronto II</t>
   </si>
   <si>
     <t>Chapecoense</t>
-  </si>
-  <si>
-    <t>Confiança</t>
   </si>
   <si>
     <t>FC Cincinnati II</t>
@@ -1448,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL123"/>
+  <dimension ref="A1:AL124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -1584,7 +1590,7 @@
         <v>110</v>
       </c>
       <c r="F2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1599,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1674,10 +1680,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL2" s="3">
         <v>45865</v>
@@ -1700,7 +1706,7 @@
         <v>111</v>
       </c>
       <c r="F3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1715,16 +1721,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L3">
-        <v>1.69</v>
+        <v>3.1</v>
       </c>
       <c r="M3">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="N3">
-        <v>3.67</v>
+        <v>1.92</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1790,10 +1796,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL3" s="3">
         <v>45865.08333333334</v>
@@ -1816,7 +1822,7 @@
         <v>112</v>
       </c>
       <c r="F4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1831,16 +1837,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L4">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="M4">
         <v>4</v>
       </c>
       <c r="N4">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1906,10 +1912,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL4" s="3">
         <v>45865.08333333334</v>
@@ -1932,7 +1938,7 @@
         <v>113</v>
       </c>
       <c r="F5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1947,16 +1953,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L5">
-        <v>3.16</v>
+        <v>1.66</v>
       </c>
       <c r="M5">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N5">
-        <v>1.93</v>
+        <v>3.8</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -2022,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL5" s="3">
         <v>45865.08333333334</v>
@@ -2048,7 +2054,7 @@
         <v>114</v>
       </c>
       <c r="F6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2063,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2138,10 +2144,10 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL6" s="3">
         <v>45865.21875</v>
@@ -2164,7 +2170,7 @@
         <v>115</v>
       </c>
       <c r="F7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2179,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2254,10 +2260,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL7" s="3">
         <v>45865.21875</v>
@@ -2280,7 +2286,7 @@
         <v>116</v>
       </c>
       <c r="F8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2295,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L8">
         <v>2.03</v>
@@ -2370,10 +2376,10 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL8" s="3">
         <v>45865.27083333334</v>
@@ -2396,7 +2402,7 @@
         <v>117</v>
       </c>
       <c r="F9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2411,16 +2417,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L9">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -2462,10 +2468,10 @@
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -2486,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL9" s="3">
         <v>45865.29166666666</v>
@@ -2506,13 +2512,13 @@
         <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
         <v>118</v>
       </c>
       <c r="F10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2527,16 +2533,16 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -2602,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL10" s="3">
         <v>45865.29166666666</v>
@@ -2628,7 +2634,7 @@
         <v>119</v>
       </c>
       <c r="F11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2643,16 +2649,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -2718,10 +2724,10 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK11" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL11" s="3">
         <v>45865.29166666666</v>
@@ -2735,16 +2741,16 @@
         <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>120</v>
       </c>
       <c r="F12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2759,16 +2765,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L12">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="M12">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="N12">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2810,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -2834,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK12" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL12" s="3">
         <v>45865.29166666666</v>
@@ -2851,7 +2857,7 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
         <v>108</v>
@@ -2860,7 +2866,7 @@
         <v>121</v>
       </c>
       <c r="F13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2875,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2950,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK13" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL13" s="3">
         <v>45865.29166666666</v>
@@ -2967,7 +2973,7 @@
         <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
         <v>108</v>
@@ -2976,7 +2982,7 @@
         <v>122</v>
       </c>
       <c r="F14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2991,16 +2997,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -3042,10 +3048,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -3066,10 +3072,10 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK14" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL14" s="3">
         <v>45865.29166666666</v>
@@ -3083,7 +3089,7 @@
         <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -3092,7 +3098,7 @@
         <v>123</v>
       </c>
       <c r="F15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3107,16 +3113,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L15">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -3182,10 +3188,10 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL15" s="3">
         <v>45865.29166666666</v>
@@ -3199,7 +3205,7 @@
         <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
         <v>108</v>
@@ -3208,7 +3214,7 @@
         <v>124</v>
       </c>
       <c r="F16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3223,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L16">
         <v>2.57</v>
@@ -3298,10 +3304,10 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK16" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL16" s="3">
         <v>45865.29166666666</v>
@@ -3324,7 +3330,7 @@
         <v>125</v>
       </c>
       <c r="F17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3339,16 +3345,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L17">
-        <v>2.9</v>
+        <v>1.25</v>
       </c>
       <c r="M17">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>2.33</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -3390,16 +3396,16 @@
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF17">
         <v>0</v>
@@ -3414,10 +3420,10 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK17" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL17" s="3">
         <v>45865.33333333334</v>
@@ -3440,7 +3446,7 @@
         <v>126</v>
       </c>
       <c r="F18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3455,16 +3461,16 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L18">
-        <v>1.25</v>
+        <v>2.9</v>
       </c>
       <c r="M18">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="N18">
-        <v>9</v>
+        <v>2.33</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -3506,16 +3512,16 @@
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD18">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF18">
         <v>0</v>
@@ -3530,10 +3536,10 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK18" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL18" s="3">
         <v>45865.33333333334</v>
@@ -3547,7 +3553,7 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
         <v>108</v>
@@ -3556,7 +3562,7 @@
         <v>127</v>
       </c>
       <c r="F19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3571,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3646,10 +3652,10 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL19" s="3">
         <v>45865.33333333334</v>
@@ -3672,7 +3678,7 @@
         <v>128</v>
       </c>
       <c r="F20" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3687,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3762,10 +3768,10 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK20" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL20" s="3">
         <v>45865.33333333334</v>
@@ -3788,7 +3794,7 @@
         <v>129</v>
       </c>
       <c r="F21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3803,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3878,10 +3884,10 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK21" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL21" s="3">
         <v>45865.35416666666</v>
@@ -3895,16 +3901,16 @@
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
         <v>130</v>
       </c>
       <c r="F22" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3919,16 +3925,16 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -3970,16 +3976,16 @@
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF22">
         <v>0</v>
@@ -3994,10 +4000,10 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK22" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL22" s="3">
         <v>45865.35416666666</v>
@@ -4020,7 +4026,7 @@
         <v>131</v>
       </c>
       <c r="F23" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4035,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -4110,10 +4116,10 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK23" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL23" s="3">
         <v>45865.35416666666</v>
@@ -4127,16 +4133,16 @@
         <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s">
         <v>132</v>
       </c>
       <c r="F24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -4151,16 +4157,16 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L24">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -4202,16 +4208,16 @@
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF24">
         <v>0</v>
@@ -4226,10 +4232,10 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK24" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL24" s="3">
         <v>45865.35416666666</v>
@@ -4243,7 +4249,7 @@
         <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
         <v>108</v>
@@ -4252,7 +4258,7 @@
         <v>133</v>
       </c>
       <c r="F25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -4267,7 +4273,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L25">
         <v>1.46</v>
@@ -4342,10 +4348,10 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK25" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL25" s="3">
         <v>45865.35763888889</v>
@@ -4359,7 +4365,7 @@
         <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
         <v>108</v>
@@ -4368,7 +4374,7 @@
         <v>134</v>
       </c>
       <c r="F26" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -4383,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L26">
         <v>1.69</v>
@@ -4458,10 +4464,10 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK26" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL26" s="3">
         <v>45865.35763888889</v>
@@ -4478,13 +4484,13 @@
         <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
         <v>135</v>
       </c>
       <c r="F27" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -4499,16 +4505,16 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4550,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD27">
         <v>0</v>
@@ -4574,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK27" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL27" s="3">
         <v>45865.375</v>
@@ -4591,7 +4597,7 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D28" t="s">
         <v>108</v>
@@ -4600,7 +4606,7 @@
         <v>136</v>
       </c>
       <c r="F28" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -4615,16 +4621,16 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L28">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="M28">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="N28">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -4666,16 +4672,16 @@
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF28">
         <v>0</v>
@@ -4690,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK28" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL28" s="3">
         <v>45865.375</v>
@@ -4710,13 +4716,13 @@
         <v>86</v>
       </c>
       <c r="D29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
         <v>137</v>
       </c>
       <c r="F29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -4731,16 +4737,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L29">
-        <v>2.92</v>
+        <v>2.16</v>
       </c>
       <c r="M29">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="N29">
-        <v>2.08</v>
+        <v>2.76</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -4785,7 +4791,7 @@
         <v>1.65</v>
       </c>
       <c r="AC29">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD29">
         <v>0</v>
@@ -4806,10 +4812,10 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK29" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL29" s="3">
         <v>45865.375</v>
@@ -4832,7 +4838,7 @@
         <v>138</v>
       </c>
       <c r="F30" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4847,16 +4853,16 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L30">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -4898,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD30">
         <v>0</v>
@@ -4922,10 +4928,10 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK30" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL30" s="3">
         <v>45865.375</v>
@@ -4939,16 +4945,16 @@
         <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
       </c>
       <c r="F31" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4963,16 +4969,16 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L31">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="M31">
-        <v>5.8</v>
+        <v>3.99</v>
       </c>
       <c r="N31">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -5014,16 +5020,16 @@
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD31">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AF31">
         <v>0</v>
@@ -5038,10 +5044,10 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK31" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL31" s="3">
         <v>45865.375</v>
@@ -5055,16 +5061,16 @@
         <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E32" t="s">
         <v>140</v>
       </c>
       <c r="F32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -5079,16 +5085,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L32">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="M32">
-        <v>3.99</v>
+        <v>3.85</v>
       </c>
       <c r="N32">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -5130,10 +5136,10 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AC32">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AD32">
         <v>0</v>
@@ -5154,10 +5160,10 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK32" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL32" s="3">
         <v>45865.375</v>
@@ -5180,7 +5186,7 @@
         <v>141</v>
       </c>
       <c r="F33" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -5195,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L33">
         <v>2</v>
@@ -5270,10 +5276,10 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK33" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL33" s="3">
         <v>45865.39583333334</v>
@@ -5287,7 +5293,7 @@
         <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -5296,7 +5302,7 @@
         <v>142</v>
       </c>
       <c r="F34" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -5311,16 +5317,16 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L34">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="M34">
-        <v>3.8</v>
+        <v>3.53</v>
       </c>
       <c r="N34">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -5365,7 +5371,7 @@
         <v>1.78</v>
       </c>
       <c r="AC34">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AD34">
         <v>0</v>
@@ -5386,10 +5392,10 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK34" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL34" s="3">
         <v>45865.39583333334</v>
@@ -5412,7 +5418,7 @@
         <v>143</v>
       </c>
       <c r="F35" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -5427,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L35">
         <v>3.82</v>
@@ -5502,10 +5508,10 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK35" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL35" s="3">
         <v>45865.39583333334</v>
@@ -5528,7 +5534,7 @@
         <v>144</v>
       </c>
       <c r="F36" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -5543,7 +5549,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L36">
         <v>1.49</v>
@@ -5618,10 +5624,10 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK36" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL36" s="3">
         <v>45865.40625</v>
@@ -5635,7 +5641,7 @@
         <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
         <v>108</v>
@@ -5644,7 +5650,7 @@
         <v>145</v>
       </c>
       <c r="F37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -5659,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L37">
         <v>2.19</v>
@@ -5734,10 +5740,10 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK37" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL37" s="3">
         <v>45865.41666666666</v>
@@ -5751,16 +5757,16 @@
         <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
       </c>
       <c r="F38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -5775,16 +5781,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L38">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N38">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5826,10 +5832,10 @@
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -5850,10 +5856,10 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK38" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL38" s="3">
         <v>45865.41666666666</v>
@@ -5867,16 +5873,16 @@
         <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
       </c>
       <c r="F39" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -5891,16 +5897,16 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -5942,10 +5948,10 @@
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -5966,10 +5972,10 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK39" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL39" s="3">
         <v>45865.41666666666</v>
@@ -5986,13 +5992,13 @@
         <v>92</v>
       </c>
       <c r="D40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E40" t="s">
         <v>148</v>
       </c>
       <c r="F40" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -6007,25 +6013,25 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L40">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="M40">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="N40">
-        <v>4.2</v>
+        <v>3.71</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P40">
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -6058,22 +6064,22 @@
         <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AC40">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AD40">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH40">
         <v>0</v>
@@ -6082,10 +6088,10 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK40" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL40" s="3">
         <v>45865.45833333334</v>
@@ -6099,7 +6105,7 @@
         <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
         <v>109</v>
@@ -6108,7 +6114,7 @@
         <v>149</v>
       </c>
       <c r="F41" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -6123,7 +6129,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L41">
         <v>1.56</v>
@@ -6198,10 +6204,10 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK41" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL41" s="3">
         <v>45865.45833333334</v>
@@ -6215,7 +6221,7 @@
         <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D42" t="s">
         <v>108</v>
@@ -6224,7 +6230,7 @@
         <v>150</v>
       </c>
       <c r="F42" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -6239,16 +6245,16 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L42">
-        <v>2.85</v>
+        <v>1.57</v>
       </c>
       <c r="M42">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N42">
-        <v>2.29</v>
+        <v>4.2</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -6290,16 +6296,16 @@
         <v>0</v>
       </c>
       <c r="AB42">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AC42">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF42">
         <v>0</v>
@@ -6314,10 +6320,10 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK42" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL42" s="3">
         <v>45865.45833333334</v>
@@ -6331,16 +6337,16 @@
         <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E43" t="s">
         <v>151</v>
       </c>
       <c r="F43" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -6355,16 +6361,16 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L43">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="M43">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="N43">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -6406,10 +6412,10 @@
         <v>0</v>
       </c>
       <c r="AB43">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC43">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD43">
         <v>0</v>
@@ -6430,10 +6436,10 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK43" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL43" s="3">
         <v>45865.45833333334</v>
@@ -6447,7 +6453,7 @@
         <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D44" t="s">
         <v>109</v>
@@ -6456,7 +6462,7 @@
         <v>152</v>
       </c>
       <c r="F44" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -6471,16 +6477,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L44">
-        <v>1.61</v>
+        <v>3.28</v>
       </c>
       <c r="M44">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="N44">
-        <v>4.7</v>
+        <v>2.32</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -6522,10 +6528,10 @@
         <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD44">
         <v>0</v>
@@ -6546,10 +6552,10 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK44" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL44" s="3">
         <v>45865.45833333334</v>
@@ -6572,7 +6578,7 @@
         <v>153</v>
       </c>
       <c r="F45" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -6587,7 +6593,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L45">
         <v>2.09</v>
@@ -6638,10 +6644,10 @@
         <v>0</v>
       </c>
       <c r="AB45">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC45">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AD45">
         <v>0</v>
@@ -6662,10 +6668,10 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK45" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL45" s="3">
         <v>45865.45833333334</v>
@@ -6679,7 +6685,7 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -6688,7 +6694,7 @@
         <v>154</v>
       </c>
       <c r="F46" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -6703,25 +6709,25 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L46">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="M46">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="N46">
-        <v>3.71</v>
+        <v>4.7</v>
       </c>
       <c r="O46">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P46">
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R46">
         <v>0</v>
@@ -6754,10 +6760,10 @@
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC46">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD46">
         <v>0</v>
@@ -6766,10 +6772,10 @@
         <v>0</v>
       </c>
       <c r="AF46">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH46">
         <v>0</v>
@@ -6778,10 +6784,10 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK46" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL46" s="3">
         <v>45865.45833333334</v>
@@ -6795,7 +6801,7 @@
         <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D47" t="s">
         <v>109</v>
@@ -6804,7 +6810,7 @@
         <v>155</v>
       </c>
       <c r="F47" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -6819,16 +6825,16 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L47">
-        <v>3.28</v>
+        <v>2.71</v>
       </c>
       <c r="M47">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="N47">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -6870,10 +6876,10 @@
         <v>0</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD47">
         <v>0</v>
@@ -6894,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="AJ47" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK47" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL47" s="3">
         <v>45865.45833333334</v>
@@ -6911,16 +6917,16 @@
         <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D48" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E48" t="s">
         <v>156</v>
       </c>
       <c r="F48" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -6935,16 +6941,16 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L48">
-        <v>4.1</v>
+        <v>2.38</v>
       </c>
       <c r="M48">
-        <v>3.88</v>
+        <v>3.33</v>
       </c>
       <c r="N48">
-        <v>1.62</v>
+        <v>2.87</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -6986,10 +6992,10 @@
         <v>0</v>
       </c>
       <c r="AB48">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC48">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD48">
         <v>0</v>
@@ -7010,10 +7016,10 @@
         <v>0</v>
       </c>
       <c r="AJ48" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK48" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL48" s="3">
         <v>45865.47916666666</v>
@@ -7027,7 +7033,7 @@
         <v>51</v>
       </c>
       <c r="C49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D49" t="s">
         <v>108</v>
@@ -7036,7 +7042,7 @@
         <v>157</v>
       </c>
       <c r="F49" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -7051,7 +7057,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L49">
         <v>1.53</v>
@@ -7126,10 +7132,10 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK49" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL49" s="3">
         <v>45865.47916666666</v>
@@ -7143,16 +7149,16 @@
         <v>51</v>
       </c>
       <c r="C50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E50" t="s">
         <v>158</v>
       </c>
       <c r="F50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -7167,16 +7173,16 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L50">
-        <v>2.38</v>
+        <v>4.1</v>
       </c>
       <c r="M50">
-        <v>3.33</v>
+        <v>3.88</v>
       </c>
       <c r="N50">
-        <v>2.87</v>
+        <v>1.62</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -7218,10 +7224,10 @@
         <v>0</v>
       </c>
       <c r="AB50">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC50">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD50">
         <v>0</v>
@@ -7242,10 +7248,10 @@
         <v>0</v>
       </c>
       <c r="AJ50" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK50" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL50" s="3">
         <v>45865.47916666666</v>
@@ -7259,16 +7265,16 @@
         <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="D51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E51" t="s">
         <v>159</v>
       </c>
       <c r="F51" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -7283,16 +7289,16 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L51">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M51">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N51">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="O51">
         <v>0</v>
@@ -7358,10 +7364,10 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK51" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL51" s="3">
         <v>45865.5</v>
@@ -7375,7 +7381,7 @@
         <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D52" t="s">
         <v>109</v>
@@ -7384,7 +7390,7 @@
         <v>160</v>
       </c>
       <c r="F52" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -7399,16 +7405,16 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L52">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="M52">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N52">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O52">
         <v>0</v>
@@ -7450,10 +7456,10 @@
         <v>0</v>
       </c>
       <c r="AB52">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC52">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD52">
         <v>0</v>
@@ -7474,10 +7480,10 @@
         <v>0</v>
       </c>
       <c r="AJ52" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK52" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL52" s="3">
         <v>45865.5</v>
@@ -7491,16 +7497,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E53" t="s">
         <v>161</v>
       </c>
       <c r="F53" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -7515,16 +7521,16 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L53">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M53">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N53">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -7566,10 +7572,10 @@
         <v>0</v>
       </c>
       <c r="AB53">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC53">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD53">
         <v>0</v>
@@ -7590,10 +7596,10 @@
         <v>0</v>
       </c>
       <c r="AJ53" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK53" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL53" s="3">
         <v>45865.5</v>
@@ -7607,7 +7613,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D54" t="s">
         <v>109</v>
@@ -7616,7 +7622,7 @@
         <v>162</v>
       </c>
       <c r="F54" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -7631,16 +7637,16 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L54">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="M54">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="N54">
-        <v>3</v>
+        <v>4.27</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -7706,10 +7712,10 @@
         <v>0</v>
       </c>
       <c r="AJ54" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK54" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL54" s="3">
         <v>45865.5</v>
@@ -7723,16 +7729,16 @@
         <v>52</v>
       </c>
       <c r="C55" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D55" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E55" t="s">
         <v>163</v>
       </c>
       <c r="F55" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -7747,16 +7753,16 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M55">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -7822,10 +7828,10 @@
         <v>0</v>
       </c>
       <c r="AJ55" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK55" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL55" s="3">
         <v>45865.5</v>
@@ -7842,13 +7848,13 @@
         <v>98</v>
       </c>
       <c r="D56" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E56" t="s">
         <v>164</v>
       </c>
       <c r="F56" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -7863,16 +7869,16 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -7914,10 +7920,10 @@
         <v>0</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD56">
         <v>0</v>
@@ -7938,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK56" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL56" s="3">
         <v>45865.5</v>
@@ -7964,7 +7970,7 @@
         <v>165</v>
       </c>
       <c r="F57" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -7979,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -8054,10 +8060,10 @@
         <v>0</v>
       </c>
       <c r="AJ57" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK57" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL57" s="3">
         <v>45865.5</v>
@@ -8071,7 +8077,7 @@
         <v>52</v>
       </c>
       <c r="C58" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D58" t="s">
         <v>109</v>
@@ -8080,7 +8086,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -8095,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -8170,10 +8176,10 @@
         <v>0</v>
       </c>
       <c r="AJ58" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK58" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL58" s="3">
         <v>45865.5</v>
@@ -8184,10 +8190,10 @@
         <v>45865</v>
       </c>
       <c r="B59" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C59" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D59" t="s">
         <v>109</v>
@@ -8196,7 +8202,7 @@
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -8211,16 +8217,16 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L59">
-        <v>1.38</v>
+        <v>3.27</v>
       </c>
       <c r="M59">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="N59">
-        <v>6.9</v>
+        <v>1.93</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -8262,10 +8268,10 @@
         <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AC59">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AD59">
         <v>0</v>
@@ -8286,13 +8292,13 @@
         <v>0</v>
       </c>
       <c r="AJ59" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK59" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL59" s="3">
-        <v>45865.52083333334</v>
+        <v>45865.5</v>
       </c>
     </row>
     <row r="60" spans="1:38">
@@ -8303,7 +8309,7 @@
         <v>53</v>
       </c>
       <c r="C60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D60" t="s">
         <v>109</v>
@@ -8312,7 +8318,7 @@
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -8327,7 +8333,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -8402,10 +8408,10 @@
         <v>0</v>
       </c>
       <c r="AJ60" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK60" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL60" s="3">
         <v>45865.52083333334</v>
@@ -8428,7 +8434,7 @@
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -8443,7 +8449,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L61">
         <v>1.91</v>
@@ -8518,10 +8524,10 @@
         <v>0</v>
       </c>
       <c r="AJ61" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK61" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL61" s="3">
         <v>45865.52083333334</v>
@@ -8532,10 +8538,10 @@
         <v>45865</v>
       </c>
       <c r="B62" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C62" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D62" t="s">
         <v>109</v>
@@ -8544,7 +8550,7 @@
         <v>170</v>
       </c>
       <c r="F62" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -8559,16 +8565,16 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L62">
-        <v>1.98</v>
+        <v>1.38</v>
       </c>
       <c r="M62">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N62">
-        <v>3.05</v>
+        <v>6.9</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -8610,16 +8616,16 @@
         <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="AC62">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AD62">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AE62">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF62">
         <v>0</v>
@@ -8634,13 +8640,13 @@
         <v>0</v>
       </c>
       <c r="AJ62" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK62" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL62" s="3">
-        <v>45865.54166666666</v>
+        <v>45865.52083333334</v>
       </c>
     </row>
     <row r="63" spans="1:38">
@@ -8651,7 +8657,7 @@
         <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="D63" t="s">
         <v>109</v>
@@ -8660,7 +8666,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -8675,85 +8681,85 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L63">
+        <v>1.62</v>
+      </c>
+      <c r="M63">
+        <v>3.54</v>
+      </c>
+      <c r="N63">
+        <v>6.2</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>1.47</v>
+      </c>
+      <c r="S63">
+        <v>2.5</v>
+      </c>
+      <c r="T63">
+        <v>3.64</v>
+      </c>
+      <c r="U63">
+        <v>1.24</v>
+      </c>
+      <c r="V63">
+        <v>9.1</v>
+      </c>
+      <c r="W63">
+        <v>1</v>
+      </c>
+      <c r="X63">
+        <v>1.04</v>
+      </c>
+      <c r="Y63">
+        <v>7.1</v>
+      </c>
+      <c r="Z63">
         <v>1.53</v>
       </c>
-      <c r="M63">
-        <v>3.5</v>
-      </c>
-      <c r="N63">
-        <v>5.5</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="Q63">
-        <v>0</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
-        <v>0</v>
-      </c>
-      <c r="T63">
-        <v>0</v>
-      </c>
-      <c r="U63">
-        <v>0</v>
-      </c>
-      <c r="V63">
-        <v>0</v>
-      </c>
-      <c r="W63">
-        <v>0</v>
-      </c>
-      <c r="X63">
-        <v>0</v>
-      </c>
-      <c r="Y63">
-        <v>0</v>
-      </c>
-      <c r="Z63">
-        <v>0</v>
-      </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB63">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="AC63">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH63">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ63" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK63" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL63" s="3">
         <v>45865.54166666666</v>
@@ -8767,7 +8773,7 @@
         <v>54</v>
       </c>
       <c r="C64" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -8776,7 +8782,7 @@
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -8791,16 +8797,16 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L64">
-        <v>2.59</v>
+        <v>1.62</v>
       </c>
       <c r="M64">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="N64">
-        <v>2.27</v>
+        <v>5.25</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -8842,16 +8848,16 @@
         <v>0</v>
       </c>
       <c r="AB64">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AC64">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AD64">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE64">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF64">
         <v>0</v>
@@ -8866,10 +8872,10 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK64" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL64" s="3">
         <v>45865.54166666666</v>
@@ -8883,7 +8889,7 @@
         <v>54</v>
       </c>
       <c r="C65" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -8892,7 +8898,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -8907,16 +8913,16 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L65">
-        <v>1.59</v>
+        <v>2.59</v>
       </c>
       <c r="M65">
-        <v>3.94</v>
+        <v>3.41</v>
       </c>
       <c r="N65">
-        <v>5.61</v>
+        <v>2.27</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -8928,64 +8934,64 @@
         <v>0</v>
       </c>
       <c r="R65">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S65">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T65">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="U65">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V65">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X65">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y65">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
         <v>1.53</v>
       </c>
-      <c r="AA65">
-        <v>2.44</v>
-      </c>
-      <c r="AB65">
-        <v>2.47</v>
-      </c>
       <c r="AC65">
-        <v>1.43</v>
+        <v>2.35</v>
       </c>
       <c r="AD65">
-        <v>5.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE65">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AF65">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AG65">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH65">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI65">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ65" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK65" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL65" s="3">
         <v>45865.54166666666</v>
@@ -8996,10 +9002,10 @@
         <v>45865</v>
       </c>
       <c r="B66" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C66" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -9008,7 +9014,7 @@
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -9023,16 +9029,16 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L66">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="M66">
-        <v>3.61</v>
+        <v>3.75</v>
       </c>
       <c r="N66">
-        <v>3.91</v>
+        <v>3.05</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -9074,16 +9080,16 @@
         <v>0</v>
       </c>
       <c r="AB66">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC66">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF66">
         <v>0</v>
@@ -9098,13 +9104,13 @@
         <v>0</v>
       </c>
       <c r="AJ66" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK66" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL66" s="3">
-        <v>45865.5625</v>
+        <v>45865.54166666666</v>
       </c>
     </row>
     <row r="67" spans="1:38">
@@ -9115,7 +9121,7 @@
         <v>55</v>
       </c>
       <c r="C67" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D67" t="s">
         <v>108</v>
@@ -9124,7 +9130,7 @@
         <v>175</v>
       </c>
       <c r="F67" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -9139,7 +9145,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L67">
         <v>0</v>
@@ -9214,10 +9220,10 @@
         <v>0</v>
       </c>
       <c r="AJ67" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK67" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL67" s="3">
         <v>45865.5625</v>
@@ -9228,10 +9234,10 @@
         <v>45865</v>
       </c>
       <c r="B68" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C68" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="D68" t="s">
         <v>109</v>
@@ -9240,7 +9246,7 @@
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -9255,16 +9261,16 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L68">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="M68">
-        <v>3.17</v>
+        <v>3.61</v>
       </c>
       <c r="N68">
-        <v>4.4</v>
+        <v>3.91</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9306,10 +9312,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="AC68">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -9330,13 +9336,13 @@
         <v>0</v>
       </c>
       <c r="AJ68" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK68" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL68" s="3">
-        <v>45865.57291666666</v>
+        <v>45865.5625</v>
       </c>
     </row>
     <row r="69" spans="1:38">
@@ -9344,10 +9350,10 @@
         <v>45865</v>
       </c>
       <c r="B69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C69" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>
@@ -9356,7 +9362,7 @@
         <v>177</v>
       </c>
       <c r="F69" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -9371,16 +9377,16 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L69">
-        <v>5.1</v>
+        <v>1.74</v>
       </c>
       <c r="M69">
-        <v>3.97</v>
+        <v>3.17</v>
       </c>
       <c r="N69">
-        <v>1.61</v>
+        <v>4.4</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -9422,10 +9428,10 @@
         <v>0</v>
       </c>
       <c r="AB69">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="AC69">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AD69">
         <v>0</v>
@@ -9446,13 +9452,13 @@
         <v>0</v>
       </c>
       <c r="AJ69" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK69" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL69" s="3">
-        <v>45865.58333333334</v>
+        <v>45865.57291666666</v>
       </c>
     </row>
     <row r="70" spans="1:38">
@@ -9463,7 +9469,7 @@
         <v>57</v>
       </c>
       <c r="C70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>
@@ -9472,7 +9478,7 @@
         <v>178</v>
       </c>
       <c r="F70" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -9487,7 +9493,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -9562,10 +9568,10 @@
         <v>0</v>
       </c>
       <c r="AJ70" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK70" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL70" s="3">
         <v>45865.58333333334</v>
@@ -9579,7 +9585,7 @@
         <v>57</v>
       </c>
       <c r="C71" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D71" t="s">
         <v>109</v>
@@ -9588,7 +9594,7 @@
         <v>179</v>
       </c>
       <c r="F71" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -9603,7 +9609,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -9678,10 +9684,10 @@
         <v>0</v>
       </c>
       <c r="AJ71" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK71" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL71" s="3">
         <v>45865.58333333334</v>
@@ -9695,7 +9701,7 @@
         <v>57</v>
       </c>
       <c r="C72" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D72" t="s">
         <v>109</v>
@@ -9704,7 +9710,7 @@
         <v>180</v>
       </c>
       <c r="F72" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -9719,7 +9725,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -9794,10 +9800,10 @@
         <v>0</v>
       </c>
       <c r="AJ72" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK72" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL72" s="3">
         <v>45865.58333333334</v>
@@ -9811,7 +9817,7 @@
         <v>57</v>
       </c>
       <c r="C73" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D73" t="s">
         <v>109</v>
@@ -9820,7 +9826,7 @@
         <v>181</v>
       </c>
       <c r="F73" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -9835,7 +9841,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -9910,10 +9916,10 @@
         <v>0</v>
       </c>
       <c r="AJ73" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK73" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL73" s="3">
         <v>45865.58333333334</v>
@@ -9927,7 +9933,7 @@
         <v>57</v>
       </c>
       <c r="C74" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D74" t="s">
         <v>109</v>
@@ -9936,7 +9942,7 @@
         <v>182</v>
       </c>
       <c r="F74" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -9951,16 +9957,16 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L74">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M74">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N74">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -10002,10 +10008,10 @@
         <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC74">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD74">
         <v>0</v>
@@ -10026,10 +10032,10 @@
         <v>0</v>
       </c>
       <c r="AJ74" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK74" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL74" s="3">
         <v>45865.58333333334</v>
@@ -10043,7 +10049,7 @@
         <v>57</v>
       </c>
       <c r="C75" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D75" t="s">
         <v>109</v>
@@ -10052,7 +10058,7 @@
         <v>183</v>
       </c>
       <c r="F75" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -10067,16 +10073,16 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L75">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -10118,10 +10124,10 @@
         <v>0</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD75">
         <v>0</v>
@@ -10142,10 +10148,10 @@
         <v>0</v>
       </c>
       <c r="AJ75" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK75" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL75" s="3">
         <v>45865.58333333334</v>
@@ -10159,7 +10165,7 @@
         <v>57</v>
       </c>
       <c r="C76" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D76" t="s">
         <v>109</v>
@@ -10168,7 +10174,7 @@
         <v>184</v>
       </c>
       <c r="F76" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -10183,7 +10189,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -10258,10 +10264,10 @@
         <v>0</v>
       </c>
       <c r="AJ76" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK76" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL76" s="3">
         <v>45865.58333333334</v>
@@ -10275,7 +10281,7 @@
         <v>57</v>
       </c>
       <c r="C77" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D77" t="s">
         <v>109</v>
@@ -10284,7 +10290,7 @@
         <v>185</v>
       </c>
       <c r="F77" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -10299,16 +10305,16 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M77">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -10350,10 +10356,10 @@
         <v>0</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD77">
         <v>0</v>
@@ -10374,10 +10380,10 @@
         <v>0</v>
       </c>
       <c r="AJ77" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK77" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL77" s="3">
         <v>45865.58333333334</v>
@@ -10388,10 +10394,10 @@
         <v>45865</v>
       </c>
       <c r="B78" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D78" t="s">
         <v>109</v>
@@ -10400,7 +10406,7 @@
         <v>186</v>
       </c>
       <c r="F78" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -10415,16 +10421,16 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L78">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M78">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N78">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -10466,10 +10472,10 @@
         <v>0</v>
       </c>
       <c r="AB78">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD78">
         <v>0</v>
@@ -10490,13 +10496,13 @@
         <v>0</v>
       </c>
       <c r="AJ78" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK78" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL78" s="3">
-        <v>45865.59375</v>
+        <v>45865.58333333334</v>
       </c>
     </row>
     <row r="79" spans="1:38">
@@ -10504,10 +10510,10 @@
         <v>45865</v>
       </c>
       <c r="B79" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C79" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="D79" t="s">
         <v>109</v>
@@ -10516,7 +10522,7 @@
         <v>187</v>
       </c>
       <c r="F79" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -10531,16 +10537,16 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L79">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M79">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -10582,10 +10588,10 @@
         <v>0</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD79">
         <v>0</v>
@@ -10606,13 +10612,13 @@
         <v>0</v>
       </c>
       <c r="AJ79" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK79" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL79" s="3">
-        <v>45865.625</v>
+        <v>45865.59375</v>
       </c>
     </row>
     <row r="80" spans="1:38">
@@ -10632,7 +10638,7 @@
         <v>188</v>
       </c>
       <c r="F80" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -10647,7 +10653,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -10722,10 +10728,10 @@
         <v>0</v>
       </c>
       <c r="AJ80" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK80" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL80" s="3">
         <v>45865.625</v>
@@ -10739,7 +10745,7 @@
         <v>59</v>
       </c>
       <c r="C81" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D81" t="s">
         <v>109</v>
@@ -10748,7 +10754,7 @@
         <v>189</v>
       </c>
       <c r="F81" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -10763,7 +10769,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -10838,10 +10844,10 @@
         <v>0</v>
       </c>
       <c r="AJ81" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK81" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL81" s="3">
         <v>45865.625</v>
@@ -10864,7 +10870,7 @@
         <v>190</v>
       </c>
       <c r="F82" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -10879,16 +10885,16 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L82">
-        <v>3.05</v>
+        <v>2.22</v>
       </c>
       <c r="M82">
         <v>2.95</v>
       </c>
       <c r="N82">
-        <v>2.31</v>
+        <v>3.2</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -10954,10 +10960,10 @@
         <v>0</v>
       </c>
       <c r="AJ82" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK82" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL82" s="3">
         <v>45865.625</v>
@@ -10971,7 +10977,7 @@
         <v>59</v>
       </c>
       <c r="C83" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="D83" t="s">
         <v>108</v>
@@ -10980,7 +10986,7 @@
         <v>191</v>
       </c>
       <c r="F83" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -10995,16 +11001,16 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L83">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M83">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -11040,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB83">
         <v>0</v>
@@ -11070,10 +11076,10 @@
         <v>0</v>
       </c>
       <c r="AJ83" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK83" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL83" s="3">
         <v>45865.625</v>
@@ -11087,16 +11093,16 @@
         <v>59</v>
       </c>
       <c r="C84" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D84" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E84" t="s">
         <v>192</v>
       </c>
       <c r="F84" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -11111,16 +11117,16 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L84">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M84">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N84">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -11186,10 +11192,10 @@
         <v>0</v>
       </c>
       <c r="AJ84" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK84" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL84" s="3">
         <v>45865.625</v>
@@ -11212,7 +11218,7 @@
         <v>193</v>
       </c>
       <c r="F85" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -11227,16 +11233,16 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L85">
-        <v>1.84</v>
+        <v>3.05</v>
       </c>
       <c r="M85">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N85">
-        <v>4.5</v>
+        <v>2.31</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11272,10 +11278,10 @@
         <v>0</v>
       </c>
       <c r="Z85">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA85">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB85">
         <v>0</v>
@@ -11302,10 +11308,10 @@
         <v>0</v>
       </c>
       <c r="AJ85" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK85" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL85" s="3">
         <v>45865.625</v>
@@ -11319,16 +11325,16 @@
         <v>59</v>
       </c>
       <c r="C86" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E86" t="s">
         <v>194</v>
       </c>
       <c r="F86" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -11343,7 +11349,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -11418,10 +11424,10 @@
         <v>0</v>
       </c>
       <c r="AJ86" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK86" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL86" s="3">
         <v>45865.625</v>
@@ -11432,10 +11438,10 @@
         <v>45865</v>
       </c>
       <c r="B87" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C87" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D87" t="s">
         <v>109</v>
@@ -11444,7 +11450,7 @@
         <v>195</v>
       </c>
       <c r="F87" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -11459,16 +11465,16 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L87">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M87">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -11516,10 +11522,10 @@
         <v>0</v>
       </c>
       <c r="AD87">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE87">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF87">
         <v>0</v>
@@ -11534,13 +11540,13 @@
         <v>0</v>
       </c>
       <c r="AJ87" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK87" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL87" s="3">
-        <v>45865.63541666666</v>
+        <v>45865.625</v>
       </c>
     </row>
     <row r="88" spans="1:38">
@@ -11551,7 +11557,7 @@
         <v>60</v>
       </c>
       <c r="C88" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D88" t="s">
         <v>109</v>
@@ -11560,7 +11566,7 @@
         <v>196</v>
       </c>
       <c r="F88" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -11575,16 +11581,16 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L88">
-        <v>9</v>
+        <v>1.35</v>
       </c>
       <c r="M88">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="N88">
-        <v>1.28</v>
+        <v>7.2</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -11626,16 +11632,16 @@
         <v>0</v>
       </c>
       <c r="AB88">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC88">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF88">
         <v>0</v>
@@ -11650,10 +11656,10 @@
         <v>0</v>
       </c>
       <c r="AJ88" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK88" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL88" s="3">
         <v>45865.63541666666</v>
@@ -11676,7 +11682,7 @@
         <v>197</v>
       </c>
       <c r="F89" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -11691,7 +11697,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L89">
         <v>3.52</v>
@@ -11766,10 +11772,10 @@
         <v>0</v>
       </c>
       <c r="AJ89" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK89" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL89" s="3">
         <v>45865.63541666666</v>
@@ -11780,19 +11786,19 @@
         <v>45865</v>
       </c>
       <c r="B90" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C90" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D90" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E90" t="s">
         <v>198</v>
       </c>
       <c r="F90" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -11807,16 +11813,16 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L90">
-        <v>2.37</v>
+        <v>6.5</v>
       </c>
       <c r="M90">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="N90">
-        <v>3.1</v>
+        <v>1.36</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -11852,16 +11858,16 @@
         <v>0</v>
       </c>
       <c r="Z90">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA90">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD90">
         <v>0</v>
@@ -11882,13 +11888,13 @@
         <v>0</v>
       </c>
       <c r="AJ90" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK90" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL90" s="3">
-        <v>45865.64583333334</v>
+        <v>45865.63541666666</v>
       </c>
     </row>
     <row r="91" spans="1:38">
@@ -11908,7 +11914,7 @@
         <v>199</v>
       </c>
       <c r="F91" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -11923,16 +11929,16 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L91">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="M91">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="N91">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -11998,10 +12004,10 @@
         <v>0</v>
       </c>
       <c r="AJ91" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK91" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL91" s="3">
         <v>45865.64583333334</v>
@@ -12024,7 +12030,7 @@
         <v>200</v>
       </c>
       <c r="F92" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -12039,16 +12045,16 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L92">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="M92">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="N92">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="O92">
         <v>0</v>
@@ -12114,10 +12120,10 @@
         <v>0</v>
       </c>
       <c r="AJ92" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK92" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL92" s="3">
         <v>45865.64583333334</v>
@@ -12131,7 +12137,7 @@
         <v>61</v>
       </c>
       <c r="C93" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D93" t="s">
         <v>109</v>
@@ -12140,7 +12146,7 @@
         <v>201</v>
       </c>
       <c r="F93" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -12155,7 +12161,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L93">
         <v>2.59</v>
@@ -12230,10 +12236,10 @@
         <v>0</v>
       </c>
       <c r="AJ93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL93" s="3">
         <v>45865.64583333334</v>
@@ -12256,7 +12262,7 @@
         <v>202</v>
       </c>
       <c r="F94" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -12271,16 +12277,16 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L94">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="M94">
-        <v>3.18</v>
+        <v>2.85</v>
       </c>
       <c r="N94">
-        <v>4.42</v>
+        <v>4.1</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -12346,10 +12352,10 @@
         <v>0</v>
       </c>
       <c r="AJ94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL94" s="3">
         <v>45865.64583333334</v>
@@ -12360,7 +12366,7 @@
         <v>45865</v>
       </c>
       <c r="B95" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C95" t="s">
         <v>103</v>
@@ -12372,7 +12378,7 @@
         <v>203</v>
       </c>
       <c r="F95" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -12387,16 +12393,16 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L95">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="M95">
-        <v>2.94</v>
+        <v>2.35</v>
       </c>
       <c r="N95">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -12432,10 +12438,10 @@
         <v>0</v>
       </c>
       <c r="Z95">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AA95">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AB95">
         <v>0</v>
@@ -12462,13 +12468,13 @@
         <v>0</v>
       </c>
       <c r="AJ95" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK95" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL95" s="3">
-        <v>45865.65277777778</v>
+        <v>45865.64583333334</v>
       </c>
     </row>
     <row r="96" spans="1:38">
@@ -12476,10 +12482,10 @@
         <v>45865</v>
       </c>
       <c r="B96" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C96" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D96" t="s">
         <v>108</v>
@@ -12488,7 +12494,7 @@
         <v>204</v>
       </c>
       <c r="F96" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -12503,16 +12509,16 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L96">
-        <v>1.46</v>
+        <v>2.55</v>
       </c>
       <c r="M96">
-        <v>3.85</v>
+        <v>2.65</v>
       </c>
       <c r="N96">
-        <v>7</v>
+        <v>2.9</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -12548,16 +12554,16 @@
         <v>0</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB96">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC96">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD96">
         <v>0</v>
@@ -12578,13 +12584,13 @@
         <v>0</v>
       </c>
       <c r="AJ96" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK96" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL96" s="3">
-        <v>45865.66666666666</v>
+        <v>45865.65277777778</v>
       </c>
     </row>
     <row r="97" spans="1:38">
@@ -12604,7 +12610,7 @@
         <v>205</v>
       </c>
       <c r="F97" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -12619,7 +12625,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -12694,10 +12700,10 @@
         <v>0</v>
       </c>
       <c r="AJ97" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK97" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL97" s="3">
         <v>45865.66666666666</v>
@@ -12711,7 +12717,7 @@
         <v>63</v>
       </c>
       <c r="C98" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D98" t="s">
         <v>108</v>
@@ -12720,7 +12726,7 @@
         <v>206</v>
       </c>
       <c r="F98" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -12735,16 +12741,16 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L98">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M98">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O98">
         <v>0</v>
@@ -12780,10 +12786,10 @@
         <v>0</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB98">
         <v>0</v>
@@ -12810,10 +12816,10 @@
         <v>0</v>
       </c>
       <c r="AJ98" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK98" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL98" s="3">
         <v>45865.66666666666</v>
@@ -12836,7 +12842,7 @@
         <v>207</v>
       </c>
       <c r="F99" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -12851,7 +12857,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L99">
         <v>1.36</v>
@@ -12926,10 +12932,10 @@
         <v>0</v>
       </c>
       <c r="AJ99" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK99" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL99" s="3">
         <v>45865.66666666666</v>
@@ -12943,7 +12949,7 @@
         <v>63</v>
       </c>
       <c r="C100" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D100" t="s">
         <v>108</v>
@@ -12952,7 +12958,7 @@
         <v>208</v>
       </c>
       <c r="F100" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -12967,16 +12973,16 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L100">
-        <v>2.15</v>
+        <v>1.46</v>
       </c>
       <c r="M100">
-        <v>3.03</v>
+        <v>3.85</v>
       </c>
       <c r="N100">
-        <v>3.08</v>
+        <v>7</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -13012,16 +13018,16 @@
         <v>0</v>
       </c>
       <c r="Z100">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA100">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB100">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC100">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AD100">
         <v>0</v>
@@ -13042,10 +13048,10 @@
         <v>0</v>
       </c>
       <c r="AJ100" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK100" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL100" s="3">
         <v>45865.66666666666</v>
@@ -13059,16 +13065,16 @@
         <v>63</v>
       </c>
       <c r="C101" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D101" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E101" t="s">
         <v>209</v>
       </c>
       <c r="F101" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -13083,16 +13089,16 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L101">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M101">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -13128,16 +13134,16 @@
         <v>0</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD101">
         <v>0</v>
@@ -13158,10 +13164,10 @@
         <v>0</v>
       </c>
       <c r="AJ101" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK101" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL101" s="3">
         <v>45865.66666666666</v>
@@ -13175,16 +13181,16 @@
         <v>63</v>
       </c>
       <c r="C102" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D102" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E102" t="s">
         <v>210</v>
       </c>
       <c r="F102" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -13199,16 +13205,16 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L102">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M102">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N102">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -13244,10 +13250,10 @@
         <v>0</v>
       </c>
       <c r="Z102">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA102">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB102">
         <v>0</v>
@@ -13274,10 +13280,10 @@
         <v>0</v>
       </c>
       <c r="AJ102" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK102" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL102" s="3">
         <v>45865.66666666666</v>
@@ -13288,10 +13294,10 @@
         <v>45865</v>
       </c>
       <c r="B103" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C103" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D103" t="s">
         <v>108</v>
@@ -13300,7 +13306,7 @@
         <v>211</v>
       </c>
       <c r="F103" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -13315,16 +13321,16 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L103">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M103">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N103">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -13372,10 +13378,10 @@
         <v>0</v>
       </c>
       <c r="AD103">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE103">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF103">
         <v>0</v>
@@ -13390,13 +13396,13 @@
         <v>0</v>
       </c>
       <c r="AJ103" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK103" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL103" s="3">
-        <v>45865.67708333334</v>
+        <v>45865.66666666666</v>
       </c>
     </row>
     <row r="104" spans="1:38">
@@ -13416,7 +13422,7 @@
         <v>212</v>
       </c>
       <c r="F104" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -13431,16 +13437,16 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L104">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M104">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N104">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O104">
         <v>0</v>
@@ -13506,10 +13512,10 @@
         <v>0</v>
       </c>
       <c r="AJ104" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK104" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL104" s="3">
         <v>45865.67708333334</v>
@@ -13532,7 +13538,7 @@
         <v>213</v>
       </c>
       <c r="F105" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -13547,16 +13553,16 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L105">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M105">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O105">
         <v>0</v>
@@ -13604,10 +13610,10 @@
         <v>0</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF105">
         <v>0</v>
@@ -13622,10 +13628,10 @@
         <v>0</v>
       </c>
       <c r="AJ105" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK105" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL105" s="3">
         <v>45865.67708333334</v>
@@ -13648,7 +13654,7 @@
         <v>214</v>
       </c>
       <c r="F106" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -13663,7 +13669,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L106">
         <v>3.1</v>
@@ -13738,10 +13744,10 @@
         <v>0</v>
       </c>
       <c r="AJ106" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK106" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL106" s="3">
         <v>45865.67708333334</v>
@@ -13752,10 +13758,10 @@
         <v>45865</v>
       </c>
       <c r="B107" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C107" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D107" t="s">
         <v>108</v>
@@ -13764,7 +13770,7 @@
         <v>215</v>
       </c>
       <c r="F107" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -13779,16 +13785,16 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L107">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M107">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -13854,13 +13860,13 @@
         <v>0</v>
       </c>
       <c r="AJ107" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK107" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL107" s="3">
-        <v>45865.6875</v>
+        <v>45865.67708333334</v>
       </c>
     </row>
     <row r="108" spans="1:38">
@@ -13880,7 +13886,7 @@
         <v>216</v>
       </c>
       <c r="F108" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -13895,7 +13901,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -13970,10 +13976,10 @@
         <v>0</v>
       </c>
       <c r="AJ108" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK108" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL108" s="3">
         <v>45865.6875</v>
@@ -13987,7 +13993,7 @@
         <v>65</v>
       </c>
       <c r="C109" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D109" t="s">
         <v>108</v>
@@ -13996,7 +14002,7 @@
         <v>217</v>
       </c>
       <c r="F109" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -14011,16 +14017,16 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L109">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M109">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O109">
         <v>0</v>
@@ -14086,10 +14092,10 @@
         <v>0</v>
       </c>
       <c r="AJ109" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK109" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL109" s="3">
         <v>45865.6875</v>
@@ -14103,7 +14109,7 @@
         <v>65</v>
       </c>
       <c r="C110" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D110" t="s">
         <v>108</v>
@@ -14112,7 +14118,7 @@
         <v>218</v>
       </c>
       <c r="F110" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -14127,16 +14133,16 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L110">
-        <v>1.57</v>
+        <v>2.24</v>
       </c>
       <c r="M110">
-        <v>3.62</v>
+        <v>2.98</v>
       </c>
       <c r="N110">
-        <v>5.91</v>
+        <v>3.17</v>
       </c>
       <c r="O110">
         <v>0</v>
@@ -14202,10 +14208,10 @@
         <v>0</v>
       </c>
       <c r="AJ110" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK110" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL110" s="3">
         <v>45865.6875</v>
@@ -14216,10 +14222,10 @@
         <v>45865</v>
       </c>
       <c r="B111" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C111" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D111" t="s">
         <v>108</v>
@@ -14228,7 +14234,7 @@
         <v>219</v>
       </c>
       <c r="F111" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -14243,16 +14249,16 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L111">
-        <v>2.31</v>
+        <v>1.69</v>
       </c>
       <c r="M111">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="N111">
-        <v>3.05</v>
+        <v>4.84</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -14288,16 +14294,16 @@
         <v>0</v>
       </c>
       <c r="Z111">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA111">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB111">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC111">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD111">
         <v>0</v>
@@ -14318,13 +14324,13 @@
         <v>0</v>
       </c>
       <c r="AJ111" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK111" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL111" s="3">
-        <v>45865.70833333334</v>
+        <v>45865.6875</v>
       </c>
     </row>
     <row r="112" spans="1:38">
@@ -14332,10 +14338,10 @@
         <v>45865</v>
       </c>
       <c r="B112" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C112" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D112" t="s">
         <v>108</v>
@@ -14344,7 +14350,7 @@
         <v>220</v>
       </c>
       <c r="F112" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -14359,16 +14365,16 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L112">
-        <v>1.59</v>
+        <v>2.31</v>
       </c>
       <c r="M112">
-        <v>3.37</v>
+        <v>2.95</v>
       </c>
       <c r="N112">
-        <v>5.1</v>
+        <v>3.05</v>
       </c>
       <c r="O112">
         <v>0</v>
@@ -14404,16 +14410,16 @@
         <v>0</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB112">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="AC112">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AD112">
         <v>0</v>
@@ -14434,13 +14440,13 @@
         <v>0</v>
       </c>
       <c r="AJ112" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK112" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL112" s="3">
-        <v>45865.77083333334</v>
+        <v>45865.70833333334</v>
       </c>
     </row>
     <row r="113" spans="1:38">
@@ -14451,7 +14457,7 @@
         <v>67</v>
       </c>
       <c r="C113" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D113" t="s">
         <v>108</v>
@@ -14460,7 +14466,7 @@
         <v>221</v>
       </c>
       <c r="F113" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -14475,16 +14481,16 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L113">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="M113">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N113">
-        <v>7.3</v>
+        <v>3.05</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -14526,10 +14532,10 @@
         <v>0</v>
       </c>
       <c r="AB113">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="AC113">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="AD113">
         <v>0</v>
@@ -14550,10 +14556,10 @@
         <v>0</v>
       </c>
       <c r="AJ113" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK113" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL113" s="3">
         <v>45865.77083333334</v>
@@ -14567,7 +14573,7 @@
         <v>67</v>
       </c>
       <c r="C114" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D114" t="s">
         <v>108</v>
@@ -14576,7 +14582,7 @@
         <v>222</v>
       </c>
       <c r="F114" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -14591,16 +14597,16 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L114">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="M114">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N114">
-        <v>3.05</v>
+        <v>7.3</v>
       </c>
       <c r="O114">
         <v>0</v>
@@ -14642,10 +14648,10 @@
         <v>0</v>
       </c>
       <c r="AB114">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="AC114">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="AD114">
         <v>0</v>
@@ -14666,10 +14672,10 @@
         <v>0</v>
       </c>
       <c r="AJ114" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK114" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL114" s="3">
         <v>45865.77083333334</v>
@@ -14680,10 +14686,10 @@
         <v>45865</v>
       </c>
       <c r="B115" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C115" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="D115" t="s">
         <v>108</v>
@@ -14692,7 +14698,7 @@
         <v>223</v>
       </c>
       <c r="F115" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -14707,16 +14713,16 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L115">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M115">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O115">
         <v>0</v>
@@ -14758,10 +14764,10 @@
         <v>0</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD115">
         <v>0</v>
@@ -14782,13 +14788,13 @@
         <v>0</v>
       </c>
       <c r="AJ115" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK115" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL115" s="3">
-        <v>45865.79166666666</v>
+        <v>45865.77083333334</v>
       </c>
     </row>
     <row r="116" spans="1:38">
@@ -14799,7 +14805,7 @@
         <v>68</v>
       </c>
       <c r="C116" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D116" t="s">
         <v>108</v>
@@ -14808,7 +14814,7 @@
         <v>224</v>
       </c>
       <c r="F116" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -14823,16 +14829,16 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L116">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M116">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N116">
-        <v>5.25</v>
+        <v>5.03</v>
       </c>
       <c r="O116">
         <v>0</v>
@@ -14874,10 +14880,10 @@
         <v>0</v>
       </c>
       <c r="AB116">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC116">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD116">
         <v>0</v>
@@ -14898,10 +14904,10 @@
         <v>0</v>
       </c>
       <c r="AJ116" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK116" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL116" s="3">
         <v>45865.79166666666</v>
@@ -14915,7 +14921,7 @@
         <v>68</v>
       </c>
       <c r="C117" t="s">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="D117" t="s">
         <v>108</v>
@@ -14924,7 +14930,7 @@
         <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -14939,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L117">
         <v>0</v>
@@ -15014,10 +15020,10 @@
         <v>0</v>
       </c>
       <c r="AJ117" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK117" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL117" s="3">
         <v>45865.79166666666</v>
@@ -15028,10 +15034,10 @@
         <v>45865</v>
       </c>
       <c r="B118" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C118" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="D118" t="s">
         <v>108</v>
@@ -15040,7 +15046,7 @@
         <v>226</v>
       </c>
       <c r="F118" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -15055,16 +15061,16 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L118">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M118">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O118">
         <v>0</v>
@@ -15106,10 +15112,10 @@
         <v>0</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD118">
         <v>0</v>
@@ -15130,13 +15136,13 @@
         <v>0</v>
       </c>
       <c r="AJ118" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK118" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL118" s="3">
-        <v>45865.83333333334</v>
+        <v>45865.79166666666</v>
       </c>
     </row>
     <row r="119" spans="1:38">
@@ -15156,7 +15162,7 @@
         <v>227</v>
       </c>
       <c r="F119" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -15171,7 +15177,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -15246,10 +15252,10 @@
         <v>0</v>
       </c>
       <c r="AJ119" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK119" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL119" s="3">
         <v>45865.83333333334</v>
@@ -15260,10 +15266,10 @@
         <v>45865</v>
       </c>
       <c r="B120" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C120" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="D120" t="s">
         <v>108</v>
@@ -15272,7 +15278,7 @@
         <v>228</v>
       </c>
       <c r="F120" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -15287,16 +15293,16 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L120">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M120">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N120">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -15332,16 +15338,16 @@
         <v>0</v>
       </c>
       <c r="Z120">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA120">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB120">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC120">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD120">
         <v>0</v>
@@ -15362,13 +15368,13 @@
         <v>0</v>
       </c>
       <c r="AJ120" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK120" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL120" s="3">
-        <v>45865.85416666666</v>
+        <v>45865.83333333334</v>
       </c>
     </row>
     <row r="121" spans="1:38">
@@ -15376,10 +15382,10 @@
         <v>45865</v>
       </c>
       <c r="B121" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C121" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D121" t="s">
         <v>108</v>
@@ -15388,7 +15394,7 @@
         <v>229</v>
       </c>
       <c r="F121" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -15403,16 +15409,16 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L121">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M121">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -15448,16 +15454,16 @@
         <v>0</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD121">
         <v>0</v>
@@ -15478,13 +15484,13 @@
         <v>0</v>
       </c>
       <c r="AJ121" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK121" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL121" s="3">
-        <v>45865.89583333334</v>
+        <v>45865.85416666666</v>
       </c>
     </row>
     <row r="122" spans="1:38">
@@ -15492,10 +15498,10 @@
         <v>45865</v>
       </c>
       <c r="B122" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C122" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="D122" t="s">
         <v>108</v>
@@ -15504,7 +15510,7 @@
         <v>230</v>
       </c>
       <c r="F122" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -15519,7 +15525,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L122">
         <v>0</v>
@@ -15594,13 +15600,13 @@
         <v>0</v>
       </c>
       <c r="AJ122" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AK122" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL122" s="3">
-        <v>45865.95833333334</v>
+        <v>45865.89583333334</v>
       </c>
     </row>
     <row r="123" spans="1:38">
@@ -15620,7 +15626,7 @@
         <v>231</v>
       </c>
       <c r="F123" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -15635,7 +15641,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L123">
         <v>0</v>
@@ -15710,12 +15716,128 @@
         <v>0</v>
       </c>
       <c r="AJ123" t="s">
+        <v>358</v>
+      </c>
+      <c r="AK123" t="s">
+        <v>358</v>
+      </c>
+      <c r="AL123" s="3">
+        <v>45865.95833333334</v>
+      </c>
+    </row>
+    <row r="124" spans="1:38">
+      <c r="A124" s="2">
+        <v>45865</v>
+      </c>
+      <c r="B124" t="s">
+        <v>72</v>
+      </c>
+      <c r="C124" t="s">
+        <v>73</v>
+      </c>
+      <c r="D124" t="s">
+        <v>108</v>
+      </c>
+      <c r="E124" t="s">
+        <v>232</v>
+      </c>
+      <c r="F124" t="s">
+        <v>355</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124" t="s">
         <v>356</v>
       </c>
-      <c r="AK123" t="s">
-        <v>356</v>
-      </c>
-      <c r="AL123" s="3">
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>0</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>0</v>
+      </c>
+      <c r="R124">
+        <v>0</v>
+      </c>
+      <c r="S124">
+        <v>0</v>
+      </c>
+      <c r="T124">
+        <v>0</v>
+      </c>
+      <c r="U124">
+        <v>0</v>
+      </c>
+      <c r="V124">
+        <v>0</v>
+      </c>
+      <c r="W124">
+        <v>0</v>
+      </c>
+      <c r="X124">
+        <v>0</v>
+      </c>
+      <c r="Y124">
+        <v>0</v>
+      </c>
+      <c r="Z124">
+        <v>0</v>
+      </c>
+      <c r="AA124">
+        <v>0</v>
+      </c>
+      <c r="AB124">
+        <v>0</v>
+      </c>
+      <c r="AC124">
+        <v>0</v>
+      </c>
+      <c r="AD124">
+        <v>0</v>
+      </c>
+      <c r="AE124">
+        <v>0</v>
+      </c>
+      <c r="AF124">
+        <v>0</v>
+      </c>
+      <c r="AG124">
+        <v>0</v>
+      </c>
+      <c r="AH124">
+        <v>0</v>
+      </c>
+      <c r="AI124">
+        <v>0</v>
+      </c>
+      <c r="AJ124" t="s">
+        <v>358</v>
+      </c>
+      <c r="AK124" t="s">
+        <v>358</v>
+      </c>
+      <c r="AL124" s="3">
         <v>45865.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-07-27.xlsx
+++ b/jogos_2025-07-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="362">
   <si>
     <t>Date</t>
   </si>
@@ -247,27 +247,27 @@
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Japan J1 League</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
-    <t>South Korea K League 1</t>
+    <t>China China League One</t>
+  </si>
+  <si>
+    <t>China Chinese Super League</t>
   </si>
   <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>China Chinese Super League</t>
-  </si>
-  <si>
-    <t>China China League One</t>
-  </si>
-  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
@@ -295,24 +295,24 @@
     <t>Switzerland Super League</t>
   </si>
   <si>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
     <t>Hungary NB I</t>
   </si>
   <si>
+    <t>Slovakia Super Liga</t>
+  </si>
+  <si>
     <t>Chile Primera División</t>
   </si>
   <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Slovakia Super Liga</t>
-  </si>
-  <si>
     <t>Hungary NB II</t>
   </si>
   <si>
@@ -322,6 +322,9 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
@@ -331,12 +334,12 @@
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
@@ -349,46 +352,52 @@
     <t>San Jose Earthquakes II</t>
   </si>
   <si>
+    <t>Rockdale City Suns</t>
+  </si>
+  <si>
+    <t>Central Coast II</t>
+  </si>
+  <si>
     <t>St. George Saints</t>
   </si>
   <si>
-    <t>Central Coast II</t>
-  </si>
-  <si>
-    <t>Rockdale City Suns</t>
+    <t>Slavia Praha II</t>
   </si>
   <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
-    <t>Slavia Praha II</t>
-  </si>
-  <si>
     <t>Yenisey</t>
   </si>
   <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Daegu</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
     <t>Urawa Reds</t>
   </si>
   <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
-    <t>Daegu</t>
-  </si>
-  <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>Seongnam</t>
+    <t>Dalian Huayi</t>
+  </si>
+  <si>
+    <t>Qingdao Jonoon</t>
   </si>
   <si>
     <t>Kalmar</t>
@@ -397,10 +406,7 @@
     <t>Changchun Yatai</t>
   </si>
   <si>
-    <t>Qingdao Jonoon</t>
-  </si>
-  <si>
-    <t>Dalian Huayi</t>
+    <t>Guangzhou E-Power</t>
   </si>
   <si>
     <t>Nantong Zhiyun</t>
@@ -409,36 +415,33 @@
     <t>RSC Anderlecht</t>
   </si>
   <si>
-    <t>Guangzhou E-Power</t>
-  </si>
-  <si>
     <t>Guangxi Baoyun</t>
   </si>
   <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
-    <t>Zhejiang FC</t>
+    <t>AIK</t>
+  </si>
+  <si>
+    <t>OB</t>
+  </si>
+  <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
   </si>
   <si>
     <t>Häcken</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
-  </si>
-  <si>
-    <t>OB</t>
-  </si>
-  <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
     <t>CSKA Moskva</t>
   </si>
   <si>
-    <t>AIK</t>
-  </si>
-  <si>
     <t>Rosenborg</t>
   </si>
   <si>
@@ -460,30 +463,30 @@
     <t>Örgryte</t>
   </si>
   <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
     <t>Lausanne Sport</t>
   </si>
   <si>
+    <t>Vestri</t>
+  </si>
+  <si>
+    <t>Neftekhimik</t>
+  </si>
+  <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
+    <t>Inter Turku</t>
+  </si>
+  <si>
     <t>Lugano</t>
   </si>
   <si>
-    <t>Inter Turku</t>
-  </si>
-  <si>
-    <t>Vestri</t>
-  </si>
-  <si>
-    <t>Neftekhimik</t>
-  </si>
-  <si>
     <t>Nyíregyháza Spartacus</t>
   </si>
   <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
     <t>Orenburg</t>
   </si>
   <si>
@@ -493,33 +496,30 @@
     <t>Värnamo</t>
   </si>
   <si>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Skalica</t>
+  </si>
+  <si>
+    <t>Podbrezová</t>
+  </si>
+  <si>
+    <t>Krasnodar</t>
+  </si>
+  <si>
     <t>Universidad Católica</t>
   </si>
   <si>
-    <t>Krasnodar</t>
+    <t>Baník Ostrava</t>
   </si>
   <si>
     <t>Turan Turkistan</t>
   </si>
   <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Podbrezová</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Videoton</t>
-  </si>
-  <si>
-    <t>Skalica</t>
-  </si>
-  <si>
     <t>Mezőkövesd-Zsóry</t>
   </si>
   <si>
@@ -529,79 +529,85 @@
     <t>CFR Cluj</t>
   </si>
   <si>
+    <t>Nordsjælland</t>
+  </si>
+  <si>
     <t>Fakel</t>
   </si>
   <si>
     <t>Arda</t>
   </si>
   <si>
-    <t>Nordsjælland</t>
-  </si>
-  <si>
     <t>Paksi SE</t>
   </si>
   <si>
     <t>O'Higgins</t>
   </si>
   <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
     <t>Club Brugge</t>
   </si>
   <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>Rubin Kazan</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Soroksár SC</t>
+  </si>
+  <si>
+    <t>BVSC</t>
+  </si>
+  <si>
+    <t>Spartak Trnava</t>
+  </si>
+  <si>
+    <t>Vasas</t>
+  </si>
+  <si>
     <t>Kozármisleny</t>
   </si>
   <si>
+    <t>Szeged 2011</t>
+  </si>
+  <si>
     <t>Budafoki MTE</t>
   </si>
   <si>
-    <t>BVSC</t>
-  </si>
-  <si>
-    <t>Vasas</t>
-  </si>
-  <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
-    <t>Rubin Kazan</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Spartak Trnava</t>
-  </si>
-  <si>
-    <t>Soroksár SC</t>
-  </si>
-  <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
+    <t>Sparta Praha</t>
+  </si>
+  <si>
+    <t>Chicago Fire II</t>
+  </si>
+  <si>
+    <t>Alvarado</t>
+  </si>
+  <si>
+    <t>Arsenal de Sarandí</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
     <t>IMT Novi Beograd</t>
   </si>
   <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
     <t>Puskás</t>
   </si>
   <si>
-    <t>Arsenal de Sarandí</t>
-  </si>
-  <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
-    <t>Sparta Praha</t>
+    <t>Septemvri Sofia</t>
   </si>
   <si>
     <t>Celje</t>
@@ -610,99 +616,99 @@
     <t>Korona Kielce</t>
   </si>
   <si>
-    <t>Septemvri Sofia</t>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Temperley</t>
   </si>
   <si>
     <t>Colegiales</t>
   </si>
   <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
     <t>Defensores Unidos</t>
   </si>
   <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
     <t>Colón</t>
   </si>
   <si>
+    <t>Palestino</t>
+  </si>
+  <si>
+    <t>Estudiantes Río Cuarto</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
     <t>Volta Redonda</t>
   </si>
   <si>
-    <t>Estudiantes Río Cuarto</t>
-  </si>
-  <si>
     <t>Cruzeiro</t>
   </si>
   <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Palestino</t>
+    <t>KR</t>
   </si>
   <si>
     <t>KA</t>
   </si>
   <si>
+    <t>Fram</t>
+  </si>
+  <si>
     <t>Valur</t>
   </si>
   <si>
-    <t>KR</t>
-  </si>
-  <si>
-    <t>Fram</t>
-  </si>
-  <si>
     <t>Caxias</t>
   </si>
   <si>
     <t>Chaco For Ever</t>
   </si>
   <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
     <t>Itabaiana</t>
   </si>
   <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
     <t>Gimnasia y Tiro</t>
   </si>
   <si>
     <t>América Mineiro</t>
   </si>
   <si>
+    <t>Internacional</t>
+  </si>
+  <si>
     <t>Bahia</t>
   </si>
   <si>
-    <t>Internacional</t>
-  </si>
-  <si>
     <t>São Bernardo</t>
   </si>
   <si>
+    <t>Atlético GO</t>
+  </si>
+  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
-    <t>Atlético GO</t>
+    <t>St. Louis City II</t>
   </si>
   <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>St. Louis City II</t>
-  </si>
-  <si>
     <t>Flamengo</t>
   </si>
   <si>
@@ -718,46 +724,52 @@
     <t>Real Monarchs</t>
   </si>
   <si>
+    <t>Sydney United</t>
+  </si>
+  <si>
+    <t>Sydney II</t>
+  </si>
+  <si>
     <t>Blacktown City</t>
   </si>
   <si>
-    <t>Sydney II</t>
-  </si>
-  <si>
-    <t>Sydney United</t>
+    <t>Líšeň</t>
   </si>
   <si>
     <t>Vyškov</t>
   </si>
   <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
     <t>SKA Khabarovsk</t>
   </si>
   <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
     <t>Avispa Fukuoka</t>
   </si>
   <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
-    <t>Jeonnam Dragons</t>
+    <t>Qingdao Red Lions</t>
+  </si>
+  <si>
+    <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Utsikten</t>
@@ -766,10 +778,7 @@
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Tianjin Teda</t>
-  </si>
-  <si>
-    <t>Qingdao Red Lions</t>
+    <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
     <t>Nanjing City</t>
@@ -778,36 +787,33 @@
     <t>KVC Westerlo</t>
   </si>
   <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
     <t>Suzhou Dongwu</t>
   </si>
   <si>
+    <t>Wuhan Three Towns</t>
+  </si>
+  <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>Wuhan Three Towns</t>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
   </si>
   <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
     <t>Akhmat Grozny</t>
   </si>
   <si>
-    <t>Öster</t>
-  </si>
-  <si>
     <t>Tromsø</t>
   </si>
   <si>
@@ -829,30 +835,30 @@
     <t>Östersunds FK</t>
   </si>
   <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
     <t>Winterthur</t>
   </si>
   <si>
+    <t>ÍBV</t>
+  </si>
+  <si>
+    <t>Torpedo Moskva</t>
+  </si>
+  <si>
+    <t>Sporting Charleroi</t>
+  </si>
+  <si>
+    <t>SJK</t>
+  </si>
+  <si>
     <t>Thun</t>
   </si>
   <si>
-    <t>SJK</t>
-  </si>
-  <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
-    <t>Torpedo Moskva</t>
-  </si>
-  <si>
     <t>Várda SE</t>
   </si>
   <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
-    <t>Sporting Charleroi</t>
-  </si>
-  <si>
     <t>Makhachkala</t>
   </si>
   <si>
@@ -862,33 +868,30 @@
     <t>Hammarby</t>
   </si>
   <si>
+    <t>Spartak Kostroma</t>
+  </si>
+  <si>
+    <t>Tychy 71</t>
+  </si>
+  <si>
+    <t>Žilina</t>
+  </si>
+  <si>
+    <t>FK Košice</t>
+  </si>
+  <si>
+    <t>Lokomotiv Moskva</t>
+  </si>
+  <si>
     <t>Coquimbo Unido</t>
   </si>
   <si>
-    <t>Lokomotiv Moskva</t>
+    <t>Teplice</t>
   </si>
   <si>
     <t>Ordabasy</t>
   </si>
   <si>
-    <t>Spartak Kostroma</t>
-  </si>
-  <si>
-    <t>Tychy 71</t>
-  </si>
-  <si>
-    <t>FK Košice</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Honvéd W</t>
-  </si>
-  <si>
-    <t>Žilina</t>
-  </si>
-  <si>
     <t>Karcag SE</t>
   </si>
   <si>
@@ -898,79 +901,85 @@
     <t>Argeș</t>
   </si>
   <si>
+    <t>Brøndby</t>
+  </si>
+  <si>
     <t>Ufa</t>
   </si>
   <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
-    <t>Brøndby</t>
-  </si>
-  <si>
     <t>Győri ETO</t>
   </si>
   <si>
     <t>Colo-Colo</t>
   </si>
   <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
     <t>KRC Genk</t>
   </si>
   <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>Zenit</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
+    <t>Békéscsaba</t>
+  </si>
+  <si>
+    <t>Ajka</t>
+  </si>
+  <si>
+    <t>Ružomberok</t>
+  </si>
+  <si>
+    <t>Csákvári TK</t>
+  </si>
+  <si>
     <t>Tiszakécske</t>
   </si>
   <si>
+    <t>Kecskeméti TE</t>
+  </si>
+  <si>
     <t>Szentlőrinc SE</t>
   </si>
   <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>Csákvári TK</t>
-  </si>
-  <si>
-    <t>Kecskeméti TE</t>
-  </si>
-  <si>
-    <t>Zenit</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>Ružomberok</t>
-  </si>
-  <si>
-    <t>Békéscsaba</t>
-  </si>
-  <si>
     <t>KAA Gent</t>
   </si>
   <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>New York RB II</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
     <t>Čukarički</t>
   </si>
   <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
     <t>Kazincbarcika</t>
   </si>
   <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>New York RB II</t>
-  </si>
-  <si>
-    <t>Mladá Boleslav</t>
+    <t>Levski Sofia</t>
   </si>
   <si>
     <t>Radomlje</t>
@@ -979,97 +988,97 @@
     <t>Legia Warszawa</t>
   </si>
   <si>
-    <t>Levski Sofia</t>
+    <t>Central Norte</t>
+  </si>
+  <si>
+    <t>Gimnasia Jujuy</t>
   </si>
   <si>
     <t>Quilmes</t>
   </si>
   <si>
+    <t>Dinamo Bucureşti</t>
+  </si>
+  <si>
     <t>Agropecuario</t>
   </si>
   <si>
-    <t>Dinamo Bucureşti</t>
-  </si>
-  <si>
-    <t>Central Norte</t>
-  </si>
-  <si>
-    <t>Gimnasia Jujuy</t>
-  </si>
-  <si>
     <t>Gimnasia Mendoza</t>
   </si>
   <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>Copiapó</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
     <t>Vila Nova</t>
   </si>
   <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
     <t>Ceará</t>
   </si>
   <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Unión Española</t>
+    <t>Breidablik</t>
   </si>
   <si>
     <t>ÍA</t>
   </si>
   <si>
+    <t>Víkingur Reykjavík</t>
+  </si>
+  <si>
     <t>FH</t>
   </si>
   <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
-    <t>Víkingur Reykjavík</t>
-  </si>
-  <si>
     <t>Ponte Preta</t>
   </si>
   <si>
     <t>Almirante Brown</t>
   </si>
   <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
     <t>Ituano</t>
   </si>
   <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
     <t>San Martín Tucumán</t>
   </si>
   <si>
     <t>Atlético PR</t>
   </si>
   <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
     <t>Juventude</t>
   </si>
   <si>
-    <t>Vasco da Gama</t>
-  </si>
-  <si>
     <t>Confiança</t>
   </si>
   <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>Chapecoense</t>
+    <t>Minnesota United II</t>
   </si>
   <si>
     <t>FC Cincinnati II</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
   </si>
   <si>
     <t>Atlético Mineiro</t>
@@ -1454,7 +1463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL124"/>
+  <dimension ref="A1:AL125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -1584,13 +1593,13 @@
         <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1605,37 +1614,37 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V2">
         <v>0</v>
@@ -1650,40 +1659,40 @@
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL2" s="3">
         <v>45865</v>
@@ -1700,13 +1709,13 @@
         <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1721,16 +1730,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L3">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="M3">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N3">
-        <v>1.92</v>
+        <v>3.8</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1796,10 +1805,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK3" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL3" s="3">
         <v>45865.08333333334</v>
@@ -1816,13 +1825,13 @@
         <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1837,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L4">
         <v>3.5</v>
@@ -1912,10 +1921,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK4" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL4" s="3">
         <v>45865.08333333334</v>
@@ -1932,13 +1941,13 @@
         <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1953,16 +1962,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L5">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N5">
-        <v>3.8</v>
+        <v>1.92</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -2028,10 +2037,10 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK5" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL5" s="3">
         <v>45865.08333333334</v>
@@ -2048,13 +2057,13 @@
         <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2069,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2144,10 +2153,10 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK6" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL6" s="3">
         <v>45865.21875</v>
@@ -2164,13 +2173,13 @@
         <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2185,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2260,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK7" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL7" s="3">
         <v>45865.21875</v>
@@ -2280,13 +2289,13 @@
         <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2301,7 +2310,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L8">
         <v>2.03</v>
@@ -2376,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL8" s="3">
         <v>45865.27083333334</v>
@@ -2396,13 +2405,13 @@
         <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2417,85 +2426,85 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ9" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK9" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL9" s="3">
         <v>45865.29166666666</v>
@@ -2509,16 +2518,16 @@
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
         <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2533,85 +2542,85 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L10">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="M10">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N10">
-        <v>5.2</v>
+        <v>3.87</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL10" s="3">
         <v>45865.29166666666</v>
@@ -2625,16 +2634,16 @@
         <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2649,85 +2658,85 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L11">
-        <v>1.67</v>
+        <v>3.36</v>
       </c>
       <c r="M11">
-        <v>3.8</v>
+        <v>3.27</v>
       </c>
       <c r="N11">
-        <v>3.87</v>
+        <v>1.93</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ11" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK11" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL11" s="3">
         <v>45865.29166666666</v>
@@ -2741,16 +2750,16 @@
         <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F12" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2765,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L12">
         <v>1.28</v>
@@ -2777,43 +2786,43 @@
         <v>8</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB12">
         <v>1.88</v>
@@ -2822,28 +2831,28 @@
         <v>1.82</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK12" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL12" s="3">
         <v>45865.29166666666</v>
@@ -2857,16 +2866,16 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2881,16 +2890,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2932,10 +2941,10 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -2956,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK13" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL13" s="3">
         <v>45865.29166666666</v>
@@ -2973,16 +2982,16 @@
         <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2997,16 +3006,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L14">
-        <v>3.5</v>
+        <v>1.45</v>
       </c>
       <c r="M14">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N14">
-        <v>1.99</v>
+        <v>5.2</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -3048,10 +3057,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -3072,10 +3081,10 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK14" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL14" s="3">
         <v>45865.29166666666</v>
@@ -3092,13 +3101,13 @@
         <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F15" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3113,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3188,10 +3197,10 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK15" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL15" s="3">
         <v>45865.29166666666</v>
@@ -3205,16 +3214,16 @@
         <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F16" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3229,16 +3238,16 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L16">
-        <v>2.57</v>
+        <v>3.92</v>
       </c>
       <c r="M16">
-        <v>3.1</v>
+        <v>3.43</v>
       </c>
       <c r="N16">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -3280,10 +3289,10 @@
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC16">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -3304,10 +3313,10 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK16" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL16" s="3">
         <v>45865.29166666666</v>
@@ -3324,13 +3333,13 @@
         <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F17" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3345,16 +3354,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L17">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -3402,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="AD17">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF17">
         <v>0</v>
@@ -3420,10 +3429,10 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK17" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL17" s="3">
         <v>45865.33333333334</v>
@@ -3440,13 +3449,13 @@
         <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F18" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3461,85 +3470,85 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L18">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="M18">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="N18">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>12.25</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AB18">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AC18">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ18" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK18" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL18" s="3">
         <v>45865.33333333334</v>
@@ -3553,16 +3562,16 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F19" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3577,85 +3586,85 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ19" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK19" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL19" s="3">
         <v>45865.33333333334</v>
@@ -3669,16 +3678,16 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F20" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3693,85 +3702,85 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ20" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK20" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL20" s="3">
         <v>45865.33333333334</v>
@@ -3785,16 +3794,16 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F21" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3809,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3884,10 +3893,10 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL21" s="3">
         <v>45865.35416666666</v>
@@ -3901,16 +3910,16 @@
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
       </c>
       <c r="E22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F22" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3925,16 +3934,16 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L22">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -3976,16 +3985,16 @@
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF22">
         <v>0</v>
@@ -4000,10 +4009,10 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK22" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL22" s="3">
         <v>45865.35416666666</v>
@@ -4017,16 +4026,16 @@
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F23" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4041,85 +4050,85 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ23" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK23" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL23" s="3">
         <v>45865.35416666666</v>
@@ -4133,16 +4142,16 @@
         <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F24" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -4157,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -4232,10 +4241,10 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK24" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL24" s="3">
         <v>45865.35416666666</v>
@@ -4252,13 +4261,13 @@
         <v>82</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F25" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -4273,85 +4282,85 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L25">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="M25">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="N25">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD25">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AE25">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AJ25" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK25" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL25" s="3">
         <v>45865.35763888889</v>
@@ -4368,13 +4377,13 @@
         <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F26" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -4389,85 +4398,85 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L26">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="M26">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="N26">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD26">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AE26">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ26" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK26" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL26" s="3">
         <v>45865.35763888889</v>
@@ -4484,13 +4493,13 @@
         <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F27" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -4505,85 +4514,85 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L27">
-        <v>2.92</v>
+        <v>1.45</v>
       </c>
       <c r="M27">
-        <v>3.39</v>
+        <v>3.85</v>
       </c>
       <c r="N27">
-        <v>2.08</v>
+        <v>5.9</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB27">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AC27">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ27" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK27" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL27" s="3">
         <v>45865.375</v>
@@ -4597,16 +4606,16 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -4621,16 +4630,16 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L28">
-        <v>1.33</v>
+        <v>2.16</v>
       </c>
       <c r="M28">
-        <v>5.8</v>
+        <v>3.41</v>
       </c>
       <c r="N28">
-        <v>6.8</v>
+        <v>2.76</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -4672,16 +4681,16 @@
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD28">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AF28">
         <v>0</v>
@@ -4696,10 +4705,10 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK28" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL28" s="3">
         <v>45865.375</v>
@@ -4713,16 +4722,16 @@
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
       </c>
       <c r="E29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F29" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -4737,85 +4746,85 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L29">
-        <v>2.16</v>
+        <v>1.33</v>
       </c>
       <c r="M29">
-        <v>3.41</v>
+        <v>5.8</v>
       </c>
       <c r="N29">
-        <v>2.76</v>
+        <v>6.8</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AB29">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="AC29">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AJ29" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK29" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL29" s="3">
         <v>45865.375</v>
@@ -4832,13 +4841,13 @@
         <v>87</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F30" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4853,16 +4862,16 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -4904,10 +4913,10 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD30">
         <v>0</v>
@@ -4928,10 +4937,10 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK30" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL30" s="3">
         <v>45865.375</v>
@@ -4945,16 +4954,16 @@
         <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
         <v>109</v>
       </c>
       <c r="E31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F31" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4969,85 +4978,85 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L31">
+        <v>2.92</v>
+      </c>
+      <c r="M31">
+        <v>3.39</v>
+      </c>
+      <c r="N31">
+        <v>2.08</v>
+      </c>
+      <c r="O31">
+        <v>2.1</v>
+      </c>
+      <c r="P31">
+        <v>11</v>
+      </c>
+      <c r="Q31">
+        <v>1.73</v>
+      </c>
+      <c r="R31">
+        <v>1.3</v>
+      </c>
+      <c r="S31">
+        <v>3.4</v>
+      </c>
+      <c r="T31">
+        <v>2.5</v>
+      </c>
+      <c r="U31">
+        <v>1.5</v>
+      </c>
+      <c r="V31">
+        <v>6</v>
+      </c>
+      <c r="W31">
+        <v>1.13</v>
+      </c>
+      <c r="X31">
+        <v>1.04</v>
+      </c>
+      <c r="Y31">
+        <v>11</v>
+      </c>
+      <c r="Z31">
+        <v>1.22</v>
+      </c>
+      <c r="AA31">
+        <v>4.33</v>
+      </c>
+      <c r="AB31">
+        <v>1.65</v>
+      </c>
+      <c r="AC31">
+        <v>2</v>
+      </c>
+      <c r="AD31">
+        <v>2.65</v>
+      </c>
+      <c r="AE31">
+        <v>1.48</v>
+      </c>
+      <c r="AF31">
         <v>1.57</v>
       </c>
-      <c r="M31">
-        <v>3.99</v>
-      </c>
-      <c r="N31">
-        <v>5.5</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="X31">
-        <v>0</v>
-      </c>
-      <c r="Y31">
-        <v>0</v>
-      </c>
-      <c r="Z31">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
-      </c>
-      <c r="AB31">
-        <v>1.98</v>
-      </c>
-      <c r="AC31">
-        <v>1.77</v>
-      </c>
-      <c r="AD31">
-        <v>0</v>
-      </c>
-      <c r="AE31">
-        <v>0</v>
-      </c>
-      <c r="AF31">
-        <v>0</v>
-      </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ31" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK31" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL31" s="3">
         <v>45865.375</v>
@@ -5061,16 +5070,16 @@
         <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F32" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -5085,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L32">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="M32">
-        <v>3.85</v>
+        <v>3.99</v>
       </c>
       <c r="N32">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -5136,10 +5145,10 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AC32">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AD32">
         <v>0</v>
@@ -5160,10 +5169,10 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK32" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL32" s="3">
         <v>45865.375</v>
@@ -5180,13 +5189,13 @@
         <v>89</v>
       </c>
       <c r="D33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F33" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -5201,7 +5210,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L33">
         <v>2</v>
@@ -5276,10 +5285,10 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK33" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL33" s="3">
         <v>45865.39583333334</v>
@@ -5293,16 +5302,16 @@
         <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F34" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -5317,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L34">
         <v>1.68</v>
@@ -5392,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK34" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL34" s="3">
         <v>45865.39583333334</v>
@@ -5412,13 +5421,13 @@
         <v>89</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F35" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -5433,7 +5442,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L35">
         <v>3.82</v>
@@ -5508,10 +5517,10 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK35" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL35" s="3">
         <v>45865.39583333334</v>
@@ -5528,13 +5537,13 @@
         <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F36" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -5549,7 +5558,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L36">
         <v>1.49</v>
@@ -5624,10 +5633,10 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK36" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL36" s="3">
         <v>45865.40625</v>
@@ -5641,16 +5650,16 @@
         <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -5665,7 +5674,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L37">
         <v>2.19</v>
@@ -5740,10 +5749,10 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK37" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL37" s="3">
         <v>45865.41666666666</v>
@@ -5760,13 +5769,13 @@
         <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E38" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F38" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -5781,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -5856,10 +5865,10 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK38" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL38" s="3">
         <v>45865.41666666666</v>
@@ -5873,16 +5882,16 @@
         <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F39" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -5897,7 +5906,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L39">
         <v>1.73</v>
@@ -5972,10 +5981,10 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK39" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL39" s="3">
         <v>45865.41666666666</v>
@@ -5989,16 +5998,16 @@
         <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E40" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -6013,25 +6022,25 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L40">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="M40">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="N40">
-        <v>3.71</v>
+        <v>4.7</v>
       </c>
       <c r="O40">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P40">
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -6064,10 +6073,10 @@
         <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC40">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD40">
         <v>0</v>
@@ -6076,10 +6085,10 @@
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH40">
         <v>0</v>
@@ -6088,10 +6097,10 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK40" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL40" s="3">
         <v>45865.45833333334</v>
@@ -6108,13 +6117,13 @@
         <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -6129,25 +6138,25 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L41">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="M41">
-        <v>3.96</v>
+        <v>3.83</v>
       </c>
       <c r="N41">
-        <v>4.4</v>
+        <v>3.71</v>
       </c>
       <c r="O41">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="P41">
         <v>0</v>
       </c>
       <c r="Q41">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -6180,10 +6189,10 @@
         <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AC41">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD41">
         <v>0</v>
@@ -6204,10 +6213,10 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK41" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL41" s="3">
         <v>45865.45833333334</v>
@@ -6224,13 +6233,13 @@
         <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F42" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -6245,16 +6254,16 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L42">
-        <v>1.57</v>
+        <v>2.85</v>
       </c>
       <c r="M42">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N42">
-        <v>4.2</v>
+        <v>2.29</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -6296,16 +6305,16 @@
         <v>0</v>
       </c>
       <c r="AB42">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC42">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AD42">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE42">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF42">
         <v>0</v>
@@ -6320,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK42" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL42" s="3">
         <v>45865.45833333334</v>
@@ -6337,16 +6346,16 @@
         <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F43" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -6361,16 +6370,16 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L43">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="M43">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="N43">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -6412,10 +6421,10 @@
         <v>0</v>
       </c>
       <c r="AB43">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD43">
         <v>0</v>
@@ -6436,10 +6445,10 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK43" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL43" s="3">
         <v>45865.45833333334</v>
@@ -6453,16 +6462,16 @@
         <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D44" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E44" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F44" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -6477,16 +6486,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L44">
-        <v>3.28</v>
+        <v>2.71</v>
       </c>
       <c r="M44">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="N44">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -6528,10 +6537,10 @@
         <v>0</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD44">
         <v>0</v>
@@ -6552,10 +6561,10 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK44" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL44" s="3">
         <v>45865.45833333334</v>
@@ -6569,16 +6578,16 @@
         <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
       </c>
       <c r="E45" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F45" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -6593,16 +6602,16 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L45">
-        <v>2.09</v>
+        <v>1.57</v>
       </c>
       <c r="M45">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N45">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -6644,16 +6653,16 @@
         <v>0</v>
       </c>
       <c r="AB45">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC45">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF45">
         <v>0</v>
@@ -6668,10 +6677,10 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK45" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL45" s="3">
         <v>45865.45833333334</v>
@@ -6685,16 +6694,16 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D46" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E46" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F46" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -6709,25 +6718,25 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L46">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="M46">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="N46">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P46">
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R46">
         <v>0</v>
@@ -6760,10 +6769,10 @@
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC46">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD46">
         <v>0</v>
@@ -6772,10 +6781,10 @@
         <v>0</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH46">
         <v>0</v>
@@ -6784,10 +6793,10 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK46" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL46" s="3">
         <v>45865.45833333334</v>
@@ -6801,16 +6810,16 @@
         <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D47" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F47" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -6825,16 +6834,16 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L47">
-        <v>2.71</v>
+        <v>2.09</v>
       </c>
       <c r="M47">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="N47">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -6876,10 +6885,10 @@
         <v>0</v>
       </c>
       <c r="AB47">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AC47">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AD47">
         <v>0</v>
@@ -6900,10 +6909,10 @@
         <v>0</v>
       </c>
       <c r="AJ47" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK47" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL47" s="3">
         <v>45865.45833333334</v>
@@ -6920,13 +6929,13 @@
         <v>88</v>
       </c>
       <c r="D48" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E48" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F48" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -6941,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L48">
         <v>2.38</v>
@@ -7016,10 +7025,10 @@
         <v>0</v>
       </c>
       <c r="AJ48" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK48" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL48" s="3">
         <v>45865.47916666666</v>
@@ -7036,13 +7045,13 @@
         <v>85</v>
       </c>
       <c r="D49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E49" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F49" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -7057,7 +7066,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L49">
         <v>1.53</v>
@@ -7132,10 +7141,10 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK49" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL49" s="3">
         <v>45865.47916666666</v>
@@ -7152,13 +7161,13 @@
         <v>85</v>
       </c>
       <c r="D50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F50" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -7173,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L50">
         <v>4.1</v>
@@ -7248,10 +7257,10 @@
         <v>0</v>
       </c>
       <c r="AJ50" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK50" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL50" s="3">
         <v>45865.47916666666</v>
@@ -7265,16 +7274,16 @@
         <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D51" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E51" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F51" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -7289,16 +7298,16 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M51">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O51">
         <v>0</v>
@@ -7364,10 +7373,10 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK51" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL51" s="3">
         <v>45865.5</v>
@@ -7381,16 +7390,16 @@
         <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D52" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E52" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F52" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -7405,16 +7414,16 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O52">
         <v>0</v>
@@ -7480,10 +7489,10 @@
         <v>0</v>
       </c>
       <c r="AJ52" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK52" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL52" s="3">
         <v>45865.5</v>
@@ -7497,16 +7506,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D53" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E53" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F53" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -7521,16 +7530,16 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -7572,10 +7581,10 @@
         <v>0</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD53">
         <v>0</v>
@@ -7596,10 +7605,10 @@
         <v>0</v>
       </c>
       <c r="AJ53" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK53" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL53" s="3">
         <v>45865.5</v>
@@ -7613,16 +7622,16 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="D54" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E54" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F54" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -7637,16 +7646,16 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L54">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="M54">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="N54">
-        <v>4.27</v>
+        <v>2.95</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -7688,10 +7697,10 @@
         <v>0</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD54">
         <v>0</v>
@@ -7712,10 +7721,10 @@
         <v>0</v>
       </c>
       <c r="AJ54" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK54" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL54" s="3">
         <v>45865.5</v>
@@ -7729,16 +7738,16 @@
         <v>52</v>
       </c>
       <c r="C55" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D55" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E55" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F55" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -7753,16 +7762,16 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L55">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M55">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N55">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -7828,10 +7837,10 @@
         <v>0</v>
       </c>
       <c r="AJ55" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK55" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL55" s="3">
         <v>45865.5</v>
@@ -7845,16 +7854,16 @@
         <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D56" t="s">
         <v>109</v>
       </c>
       <c r="E56" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F56" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -7869,16 +7878,16 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L56">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M56">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N56">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -7920,10 +7929,10 @@
         <v>0</v>
       </c>
       <c r="AB56">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC56">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD56">
         <v>0</v>
@@ -7944,10 +7953,10 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK56" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL56" s="3">
         <v>45865.5</v>
@@ -7964,13 +7973,13 @@
         <v>91</v>
       </c>
       <c r="D57" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E57" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F57" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -7985,7 +7994,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -8060,10 +8069,10 @@
         <v>0</v>
       </c>
       <c r="AJ57" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK57" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL57" s="3">
         <v>45865.5</v>
@@ -8077,16 +8086,16 @@
         <v>52</v>
       </c>
       <c r="C58" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D58" t="s">
         <v>109</v>
       </c>
       <c r="E58" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F58" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -8101,7 +8110,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -8176,10 +8185,10 @@
         <v>0</v>
       </c>
       <c r="AJ58" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK58" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL58" s="3">
         <v>45865.5</v>
@@ -8190,19 +8199,19 @@
         <v>45865</v>
       </c>
       <c r="B59" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C59" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D59" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E59" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F59" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -8217,16 +8226,16 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L59">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="M59">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N59">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -8268,10 +8277,10 @@
         <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC59">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD59">
         <v>0</v>
@@ -8292,13 +8301,13 @@
         <v>0</v>
       </c>
       <c r="AJ59" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK59" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL59" s="3">
-        <v>45865.5</v>
+        <v>45865.52083333334</v>
       </c>
     </row>
     <row r="60" spans="1:38">
@@ -8309,16 +8318,16 @@
         <v>53</v>
       </c>
       <c r="C60" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D60" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E60" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F60" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -8333,16 +8342,16 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -8384,10 +8393,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD60">
         <v>0</v>
@@ -8408,10 +8417,10 @@
         <v>0</v>
       </c>
       <c r="AJ60" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK60" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL60" s="3">
         <v>45865.52083333334</v>
@@ -8425,16 +8434,16 @@
         <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D61" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E61" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F61" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -8449,16 +8458,16 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L61">
-        <v>1.91</v>
+        <v>1.38</v>
       </c>
       <c r="M61">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="N61">
-        <v>3.34</v>
+        <v>6.9</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -8500,10 +8509,10 @@
         <v>0</v>
       </c>
       <c r="AB61">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AC61">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AD61">
         <v>0</v>
@@ -8524,10 +8533,10 @@
         <v>0</v>
       </c>
       <c r="AJ61" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK61" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL61" s="3">
         <v>45865.52083333334</v>
@@ -8538,19 +8547,19 @@
         <v>45865</v>
       </c>
       <c r="B62" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C62" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E62" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F62" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -8565,16 +8574,16 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L62">
-        <v>1.38</v>
+        <v>2.59</v>
       </c>
       <c r="M62">
-        <v>4</v>
+        <v>3.41</v>
       </c>
       <c r="N62">
-        <v>6.9</v>
+        <v>2.27</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -8616,16 +8625,16 @@
         <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AC62">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF62">
         <v>0</v>
@@ -8640,13 +8649,13 @@
         <v>0</v>
       </c>
       <c r="AJ62" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK62" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL62" s="3">
-        <v>45865.52083333334</v>
+        <v>45865.54166666666</v>
       </c>
     </row>
     <row r="63" spans="1:38">
@@ -8660,13 +8669,13 @@
         <v>76</v>
       </c>
       <c r="D63" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E63" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F63" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -8681,7 +8690,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L63">
         <v>1.62</v>
@@ -8756,10 +8765,10 @@
         <v>1.02</v>
       </c>
       <c r="AJ63" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK63" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL63" s="3">
         <v>45865.54166666666</v>
@@ -8776,13 +8785,13 @@
         <v>101</v>
       </c>
       <c r="D64" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E64" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F64" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -8797,16 +8806,16 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L64">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M64">
         <v>3.5</v>
       </c>
       <c r="N64">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -8872,10 +8881,10 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK64" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL64" s="3">
         <v>45865.54166666666</v>
@@ -8889,16 +8898,16 @@
         <v>54</v>
       </c>
       <c r="C65" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D65" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E65" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F65" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -8913,16 +8922,16 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L65">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
       <c r="M65">
-        <v>3.41</v>
+        <v>3.64</v>
       </c>
       <c r="N65">
-        <v>2.27</v>
+        <v>2.92</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -8970,10 +8979,10 @@
         <v>2.35</v>
       </c>
       <c r="AD65">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AE65">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AF65">
         <v>0</v>
@@ -8988,10 +8997,10 @@
         <v>0</v>
       </c>
       <c r="AJ65" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK65" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL65" s="3">
         <v>45865.54166666666</v>
@@ -9002,19 +9011,19 @@
         <v>45865</v>
       </c>
       <c r="B66" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C66" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
       </c>
       <c r="E66" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F66" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -9029,16 +9038,16 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L66">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M66">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N66">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -9080,16 +9089,16 @@
         <v>0</v>
       </c>
       <c r="AB66">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC66">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD66">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AE66">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF66">
         <v>0</v>
@@ -9104,13 +9113,13 @@
         <v>0</v>
       </c>
       <c r="AJ66" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK66" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL66" s="3">
-        <v>45865.54166666666</v>
+        <v>45865.5625</v>
       </c>
     </row>
     <row r="67" spans="1:38">
@@ -9121,16 +9130,16 @@
         <v>55</v>
       </c>
       <c r="C67" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D67" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E67" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F67" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -9145,16 +9154,16 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -9196,10 +9205,10 @@
         <v>0</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD67">
         <v>0</v>
@@ -9220,10 +9229,10 @@
         <v>0</v>
       </c>
       <c r="AJ67" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK67" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL67" s="3">
         <v>45865.5625</v>
@@ -9240,13 +9249,13 @@
         <v>84</v>
       </c>
       <c r="D68" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E68" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F68" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -9261,7 +9270,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L68">
         <v>1.71</v>
@@ -9336,10 +9345,10 @@
         <v>0</v>
       </c>
       <c r="AJ68" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK68" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL68" s="3">
         <v>45865.5625</v>
@@ -9356,13 +9365,13 @@
         <v>101</v>
       </c>
       <c r="D69" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E69" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F69" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -9377,7 +9386,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L69">
         <v>1.74</v>
@@ -9452,10 +9461,10 @@
         <v>0</v>
       </c>
       <c r="AJ69" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK69" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL69" s="3">
         <v>45865.57291666666</v>
@@ -9469,16 +9478,16 @@
         <v>57</v>
       </c>
       <c r="C70" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D70" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E70" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F70" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -9493,16 +9502,16 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -9544,10 +9553,10 @@
         <v>0</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD70">
         <v>0</v>
@@ -9568,10 +9577,10 @@
         <v>0</v>
       </c>
       <c r="AJ70" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK70" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL70" s="3">
         <v>45865.58333333334</v>
@@ -9585,16 +9594,16 @@
         <v>57</v>
       </c>
       <c r="C71" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D71" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E71" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F71" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -9609,16 +9618,16 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L71">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M71">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -9660,10 +9669,10 @@
         <v>0</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD71">
         <v>0</v>
@@ -9684,10 +9693,10 @@
         <v>0</v>
       </c>
       <c r="AJ71" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK71" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL71" s="3">
         <v>45865.58333333334</v>
@@ -9704,13 +9713,13 @@
         <v>99</v>
       </c>
       <c r="D72" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E72" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F72" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -9725,7 +9734,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -9800,10 +9809,10 @@
         <v>0</v>
       </c>
       <c r="AJ72" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK72" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL72" s="3">
         <v>45865.58333333334</v>
@@ -9820,13 +9829,13 @@
         <v>99</v>
       </c>
       <c r="D73" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E73" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F73" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -9841,7 +9850,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -9916,10 +9925,10 @@
         <v>0</v>
       </c>
       <c r="AJ73" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK73" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL73" s="3">
         <v>45865.58333333334</v>
@@ -9933,16 +9942,16 @@
         <v>57</v>
       </c>
       <c r="C74" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D74" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E74" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F74" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -9957,16 +9966,16 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M74">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -10008,10 +10017,10 @@
         <v>0</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD74">
         <v>0</v>
@@ -10032,10 +10041,10 @@
         <v>0</v>
       </c>
       <c r="AJ74" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK74" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL74" s="3">
         <v>45865.58333333334</v>
@@ -10049,16 +10058,16 @@
         <v>57</v>
       </c>
       <c r="C75" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D75" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E75" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F75" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -10073,16 +10082,16 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L75">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M75">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N75">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -10124,10 +10133,10 @@
         <v>0</v>
       </c>
       <c r="AB75">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC75">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD75">
         <v>0</v>
@@ -10148,10 +10157,10 @@
         <v>0</v>
       </c>
       <c r="AJ75" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK75" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL75" s="3">
         <v>45865.58333333334</v>
@@ -10165,16 +10174,16 @@
         <v>57</v>
       </c>
       <c r="C76" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D76" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E76" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F76" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -10189,7 +10198,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -10264,10 +10273,10 @@
         <v>0</v>
       </c>
       <c r="AJ76" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK76" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL76" s="3">
         <v>45865.58333333334</v>
@@ -10281,16 +10290,16 @@
         <v>57</v>
       </c>
       <c r="C77" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D77" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E77" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F77" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -10305,16 +10314,16 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L77">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M77">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N77">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -10356,10 +10365,10 @@
         <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC77">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD77">
         <v>0</v>
@@ -10380,10 +10389,10 @@
         <v>0</v>
       </c>
       <c r="AJ77" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK77" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL77" s="3">
         <v>45865.58333333334</v>
@@ -10400,13 +10409,13 @@
         <v>99</v>
       </c>
       <c r="D78" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E78" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F78" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -10421,7 +10430,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -10496,10 +10505,10 @@
         <v>0</v>
       </c>
       <c r="AJ78" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK78" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL78" s="3">
         <v>45865.58333333334</v>
@@ -10516,13 +10525,13 @@
         <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E79" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F79" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -10537,7 +10546,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L79">
         <v>2.26</v>
@@ -10612,10 +10621,10 @@
         <v>0</v>
       </c>
       <c r="AJ79" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK79" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL79" s="3">
         <v>45865.59375</v>
@@ -10629,16 +10638,16 @@
         <v>59</v>
       </c>
       <c r="C80" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D80" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E80" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F80" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -10653,7 +10662,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -10728,10 +10737,10 @@
         <v>0</v>
       </c>
       <c r="AJ80" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK80" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL80" s="3">
         <v>45865.625</v>
@@ -10745,16 +10754,16 @@
         <v>59</v>
       </c>
       <c r="C81" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="D81" t="s">
         <v>109</v>
       </c>
       <c r="E81" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F81" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -10769,7 +10778,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -10844,10 +10853,10 @@
         <v>0</v>
       </c>
       <c r="AJ81" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK81" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL81" s="3">
         <v>45865.625</v>
@@ -10861,16 +10870,16 @@
         <v>59</v>
       </c>
       <c r="C82" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D82" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E82" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F82" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -10885,16 +10894,16 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L82">
-        <v>2.22</v>
+        <v>2.57</v>
       </c>
       <c r="M82">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="N82">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -10960,10 +10969,10 @@
         <v>0</v>
       </c>
       <c r="AJ82" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK82" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL82" s="3">
         <v>45865.625</v>
@@ -10977,16 +10986,16 @@
         <v>59</v>
       </c>
       <c r="C83" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D83" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E83" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F83" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -11001,16 +11010,16 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L83">
-        <v>1.84</v>
+        <v>3.05</v>
       </c>
       <c r="M83">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N83">
-        <v>4.5</v>
+        <v>2.31</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -11046,10 +11055,10 @@
         <v>0</v>
       </c>
       <c r="Z83">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA83">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB83">
         <v>0</v>
@@ -11076,10 +11085,10 @@
         <v>0</v>
       </c>
       <c r="AJ83" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK83" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL83" s="3">
         <v>45865.625</v>
@@ -11093,16 +11102,16 @@
         <v>59</v>
       </c>
       <c r="C84" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D84" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E84" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F84" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -11117,16 +11126,16 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L84">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M84">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -11168,10 +11177,10 @@
         <v>0</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD84">
         <v>0</v>
@@ -11192,10 +11201,10 @@
         <v>0</v>
       </c>
       <c r="AJ84" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK84" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL84" s="3">
         <v>45865.625</v>
@@ -11209,16 +11218,16 @@
         <v>59</v>
       </c>
       <c r="C85" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D85" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E85" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F85" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -11233,16 +11242,16 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="L85">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="M85">
-        <v>2.95</v>
+        <v>2.56</v>
       </c>
       <c r="N85">
-        <v>2.31</v>
+        <v>4.3</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11278,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB85">
         <v>0</v>
@@ -11308,10 +11317,10 @@
         <v>0</v>
       </c>
       <c r="AJ85" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK85" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL85" s="3">
         <v>45865.625</v>
@@ -11325,16 +11334,16 @@
         <v>59</v>
       </c>
       <c r="C86" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="D86" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E86" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F86" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -11349,16 +11358,16 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -11400,10 +11409,10 @@
         <v>0</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD86">
         <v>0</v>
@@ -11424,10 +11433,10 @@
         <v>0</v>
       </c>
       <c r="AJ86" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK86" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL86" s="3">
         <v>45865.625</v>
@@ -11441,16 +11450,16 @@
         <v>59</v>
       </c>
       <c r="C87" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D87" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E87" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F87" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -11465,7 +11474,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -11540,10 +11549,10 @@
         <v>0</v>
       </c>
       <c r="AJ87" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK87" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL87" s="3">
         <v>45865.625</v>
@@ -11557,16 +11566,16 @@
         <v>60</v>
       </c>
       <c r="C88" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D88" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E88" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F88" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -11581,16 +11590,16 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L88">
-        <v>1.35</v>
+        <v>6.5</v>
       </c>
       <c r="M88">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="N88">
-        <v>7.2</v>
+        <v>1.36</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -11632,16 +11641,16 @@
         <v>0</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD88">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE88">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF88">
         <v>0</v>
@@ -11656,10 +11665,10 @@
         <v>0</v>
       </c>
       <c r="AJ88" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK88" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL88" s="3">
         <v>45865.63541666666</v>
@@ -11673,16 +11682,16 @@
         <v>60</v>
       </c>
       <c r="C89" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D89" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E89" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F89" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -11697,16 +11706,16 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L89">
-        <v>3.52</v>
+        <v>1.35</v>
       </c>
       <c r="M89">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N89">
-        <v>1.86</v>
+        <v>7.2</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -11748,16 +11757,16 @@
         <v>0</v>
       </c>
       <c r="AB89">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC89">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF89">
         <v>0</v>
@@ -11772,10 +11781,10 @@
         <v>0</v>
       </c>
       <c r="AJ89" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK89" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL89" s="3">
         <v>45865.63541666666</v>
@@ -11789,16 +11798,16 @@
         <v>60</v>
       </c>
       <c r="C90" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D90" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E90" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F90" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -11813,16 +11822,16 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L90">
-        <v>6.5</v>
+        <v>3.52</v>
       </c>
       <c r="M90">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="N90">
-        <v>1.36</v>
+        <v>1.86</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -11864,10 +11873,10 @@
         <v>0</v>
       </c>
       <c r="AB90">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC90">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AD90">
         <v>0</v>
@@ -11888,10 +11897,10 @@
         <v>0</v>
       </c>
       <c r="AJ90" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK90" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL90" s="3">
         <v>45865.63541666666</v>
@@ -11905,16 +11914,16 @@
         <v>61</v>
       </c>
       <c r="C91" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D91" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E91" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F91" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -11929,16 +11938,16 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="L91">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="M91">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="N91">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -11974,10 +11983,10 @@
         <v>0</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB91">
         <v>0</v>
@@ -12004,10 +12013,10 @@
         <v>0</v>
       </c>
       <c r="AJ91" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK91" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL91" s="3">
         <v>45865.64583333334</v>
@@ -12021,16 +12030,16 @@
         <v>61</v>
       </c>
       <c r="C92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D92" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E92" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F92" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -12045,16 +12054,16 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L92">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="M92">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="N92">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="O92">
         <v>0</v>
@@ -12090,10 +12099,10 @@
         <v>0</v>
       </c>
       <c r="Z92">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AA92">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AB92">
         <v>0</v>
@@ -12120,10 +12129,10 @@
         <v>0</v>
       </c>
       <c r="AJ92" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK92" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL92" s="3">
         <v>45865.64583333334</v>
@@ -12137,16 +12146,16 @@
         <v>61</v>
       </c>
       <c r="C93" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D93" t="s">
         <v>109</v>
       </c>
       <c r="E93" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F93" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -12161,17 +12170,17 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L93">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="M93">
+        <v>2.6</v>
+      </c>
+      <c r="N93">
         <v>2.9</v>
       </c>
-      <c r="N93">
-        <v>2.58</v>
-      </c>
       <c r="O93">
         <v>0</v>
       </c>
@@ -12206,16 +12215,16 @@
         <v>0</v>
       </c>
       <c r="Z93">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA93">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB93">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC93">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD93">
         <v>0</v>
@@ -12236,10 +12245,10 @@
         <v>0</v>
       </c>
       <c r="AJ93" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK93" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL93" s="3">
         <v>45865.64583333334</v>
@@ -12253,16 +12262,16 @@
         <v>61</v>
       </c>
       <c r="C94" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D94" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E94" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F94" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -12277,16 +12286,16 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L94">
-        <v>1.9</v>
+        <v>2.59</v>
       </c>
       <c r="M94">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N94">
-        <v>4.1</v>
+        <v>2.58</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -12322,17 +12331,17 @@
         <v>0</v>
       </c>
       <c r="Z94">
+        <v>1.55</v>
+      </c>
+      <c r="AA94">
+        <v>2.45</v>
+      </c>
+      <c r="AB94">
+        <v>2.35</v>
+      </c>
+      <c r="AC94">
         <v>1.53</v>
       </c>
-      <c r="AA94">
-        <v>2.3</v>
-      </c>
-      <c r="AB94">
-        <v>0</v>
-      </c>
-      <c r="AC94">
-        <v>0</v>
-      </c>
       <c r="AD94">
         <v>0</v>
       </c>
@@ -12352,10 +12361,10 @@
         <v>0</v>
       </c>
       <c r="AJ94" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK94" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL94" s="3">
         <v>45865.64583333334</v>
@@ -12369,16 +12378,16 @@
         <v>61</v>
       </c>
       <c r="C95" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D95" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E95" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F95" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -12393,16 +12402,16 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L95">
-        <v>2.7</v>
+        <v>3.26</v>
       </c>
       <c r="M95">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="N95">
-        <v>3.1</v>
+        <v>2.16</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -12438,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Z95">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AA95">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AB95">
         <v>0</v>
@@ -12468,10 +12477,10 @@
         <v>0</v>
       </c>
       <c r="AJ95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL95" s="3">
         <v>45865.64583333334</v>
@@ -12485,16 +12494,16 @@
         <v>62</v>
       </c>
       <c r="C96" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D96" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E96" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F96" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -12509,16 +12518,16 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L96">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="M96">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N96">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -12584,10 +12593,10 @@
         <v>0</v>
       </c>
       <c r="AJ96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL96" s="3">
         <v>45865.65277777778</v>
@@ -12601,16 +12610,16 @@
         <v>63</v>
       </c>
       <c r="C97" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D97" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E97" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F97" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -12625,7 +12634,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -12700,10 +12709,10 @@
         <v>0</v>
       </c>
       <c r="AJ97" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK97" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL97" s="3">
         <v>45865.66666666666</v>
@@ -12717,16 +12726,16 @@
         <v>63</v>
       </c>
       <c r="C98" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D98" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E98" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F98" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -12741,13 +12750,13 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L98">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="M98">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N98">
         <v>4.5</v>
@@ -12816,10 +12825,10 @@
         <v>0</v>
       </c>
       <c r="AJ98" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK98" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL98" s="3">
         <v>45865.66666666666</v>
@@ -12833,16 +12842,16 @@
         <v>63</v>
       </c>
       <c r="C99" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D99" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E99" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F99" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -12857,16 +12866,16 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L99">
-        <v>1.36</v>
+        <v>2.99</v>
       </c>
       <c r="M99">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="N99">
-        <v>7.3</v>
+        <v>2.04</v>
       </c>
       <c r="O99">
         <v>0</v>
@@ -12902,16 +12911,16 @@
         <v>0</v>
       </c>
       <c r="Z99">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA99">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AB99">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC99">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD99">
         <v>0</v>
@@ -12932,10 +12941,10 @@
         <v>0</v>
       </c>
       <c r="AJ99" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK99" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL99" s="3">
         <v>45865.66666666666</v>
@@ -12949,16 +12958,16 @@
         <v>63</v>
       </c>
       <c r="C100" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D100" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E100" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F100" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -12973,16 +12982,16 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L100">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="M100">
-        <v>3.85</v>
+        <v>3.03</v>
       </c>
       <c r="N100">
-        <v>7</v>
+        <v>3.08</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -13018,16 +13027,16 @@
         <v>0</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB100">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC100">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AD100">
         <v>0</v>
@@ -13048,10 +13057,10 @@
         <v>0</v>
       </c>
       <c r="AJ100" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK100" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL100" s="3">
         <v>45865.66666666666</v>
@@ -13065,16 +13074,16 @@
         <v>63</v>
       </c>
       <c r="C101" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D101" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E101" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F101" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -13089,16 +13098,16 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L101">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="M101">
-        <v>3.03</v>
+        <v>3.3</v>
       </c>
       <c r="N101">
-        <v>3.08</v>
+        <v>2.37</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -13134,16 +13143,16 @@
         <v>0</v>
       </c>
       <c r="Z101">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA101">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB101">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AC101">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD101">
         <v>0</v>
@@ -13164,10 +13173,10 @@
         <v>0</v>
       </c>
       <c r="AJ101" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK101" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL101" s="3">
         <v>45865.66666666666</v>
@@ -13181,16 +13190,16 @@
         <v>63</v>
       </c>
       <c r="C102" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D102" t="s">
         <v>109</v>
       </c>
       <c r="E102" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F102" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -13205,16 +13214,16 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L102">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M102">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -13256,10 +13265,10 @@
         <v>0</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD102">
         <v>0</v>
@@ -13280,10 +13289,10 @@
         <v>0</v>
       </c>
       <c r="AJ102" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK102" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL102" s="3">
         <v>45865.66666666666</v>
@@ -13297,16 +13306,16 @@
         <v>63</v>
       </c>
       <c r="C103" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D103" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E103" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F103" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -13321,7 +13330,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -13396,10 +13405,10 @@
         <v>0</v>
       </c>
       <c r="AJ103" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK103" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL103" s="3">
         <v>45865.66666666666</v>
@@ -13410,19 +13419,19 @@
         <v>45865</v>
       </c>
       <c r="B104" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C104" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D104" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E104" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F104" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -13437,16 +13446,16 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L104">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M104">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O104">
         <v>0</v>
@@ -13482,16 +13491,16 @@
         <v>0</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD104">
         <v>0</v>
@@ -13512,13 +13521,13 @@
         <v>0</v>
       </c>
       <c r="AJ104" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK104" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL104" s="3">
-        <v>45865.67708333334</v>
+        <v>45865.66666666666</v>
       </c>
     </row>
     <row r="105" spans="1:38">
@@ -13529,16 +13538,16 @@
         <v>64</v>
       </c>
       <c r="C105" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D105" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E105" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F105" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -13553,16 +13562,16 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L105">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="M105">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N105">
-        <v>4</v>
+        <v>1.95</v>
       </c>
       <c r="O105">
         <v>0</v>
@@ -13610,10 +13619,10 @@
         <v>0</v>
       </c>
       <c r="AD105">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AE105">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AF105">
         <v>0</v>
@@ -13628,10 +13637,10 @@
         <v>0</v>
       </c>
       <c r="AJ105" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK105" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL105" s="3">
         <v>45865.67708333334</v>
@@ -13645,16 +13654,16 @@
         <v>64</v>
       </c>
       <c r="C106" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D106" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E106" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F106" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -13669,16 +13678,16 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L106">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M106">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N106">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O106">
         <v>0</v>
@@ -13726,10 +13735,10 @@
         <v>0</v>
       </c>
       <c r="AD106">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE106">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF106">
         <v>0</v>
@@ -13744,10 +13753,10 @@
         <v>0</v>
       </c>
       <c r="AJ106" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK106" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL106" s="3">
         <v>45865.67708333334</v>
@@ -13761,16 +13770,16 @@
         <v>64</v>
       </c>
       <c r="C107" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D107" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E107" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F107" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -13785,7 +13794,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L107">
         <v>3.6</v>
@@ -13842,10 +13851,10 @@
         <v>0</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF107">
         <v>0</v>
@@ -13860,10 +13869,10 @@
         <v>0</v>
       </c>
       <c r="AJ107" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK107" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL107" s="3">
         <v>45865.67708333334</v>
@@ -13874,19 +13883,19 @@
         <v>45865</v>
       </c>
       <c r="B108" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C108" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D108" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E108" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F108" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -13901,16 +13910,16 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L108">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M108">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O108">
         <v>0</v>
@@ -13958,10 +13967,10 @@
         <v>0</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF108">
         <v>0</v>
@@ -13976,13 +13985,13 @@
         <v>0</v>
       </c>
       <c r="AJ108" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK108" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL108" s="3">
-        <v>45865.6875</v>
+        <v>45865.67708333334</v>
       </c>
     </row>
     <row r="109" spans="1:38">
@@ -13993,16 +14002,16 @@
         <v>65</v>
       </c>
       <c r="C109" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D109" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E109" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F109" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -14017,16 +14026,16 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L109">
-        <v>1.68</v>
+        <v>2.31</v>
       </c>
       <c r="M109">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N109">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="O109">
         <v>0</v>
@@ -14092,10 +14101,10 @@
         <v>0</v>
       </c>
       <c r="AJ109" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK109" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL109" s="3">
         <v>45865.6875</v>
@@ -14109,16 +14118,16 @@
         <v>65</v>
       </c>
       <c r="C110" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D110" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E110" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F110" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -14133,16 +14142,16 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="L110">
-        <v>2.24</v>
+        <v>1.78</v>
       </c>
       <c r="M110">
-        <v>2.98</v>
+        <v>2.66</v>
       </c>
       <c r="N110">
-        <v>3.17</v>
+        <v>5.5</v>
       </c>
       <c r="O110">
         <v>0</v>
@@ -14208,10 +14217,10 @@
         <v>0</v>
       </c>
       <c r="AJ110" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK110" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL110" s="3">
         <v>45865.6875</v>
@@ -14225,16 +14234,16 @@
         <v>65</v>
       </c>
       <c r="C111" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D111" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E111" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F111" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -14249,7 +14258,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L111">
         <v>1.69</v>
@@ -14300,10 +14309,10 @@
         <v>0</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD111">
         <v>0</v>
@@ -14324,10 +14333,10 @@
         <v>0</v>
       </c>
       <c r="AJ111" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK111" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL111" s="3">
         <v>45865.6875</v>
@@ -14338,19 +14347,19 @@
         <v>45865</v>
       </c>
       <c r="B112" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C112" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D112" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E112" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F112" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -14365,16 +14374,16 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L112">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="M112">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="N112">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="O112">
         <v>0</v>
@@ -14410,16 +14419,16 @@
         <v>0</v>
       </c>
       <c r="Z112">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA112">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB112">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC112">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD112">
         <v>0</v>
@@ -14440,13 +14449,13 @@
         <v>0</v>
       </c>
       <c r="AJ112" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK112" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL112" s="3">
-        <v>45865.70833333334</v>
+        <v>45865.6875</v>
       </c>
     </row>
     <row r="113" spans="1:38">
@@ -14454,19 +14463,19 @@
         <v>45865</v>
       </c>
       <c r="B113" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C113" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D113" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E113" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F113" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -14481,16 +14490,16 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L113">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="M113">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="N113">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -14526,16 +14535,16 @@
         <v>0</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB113">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC113">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AD113">
         <v>0</v>
@@ -14556,13 +14565,13 @@
         <v>0</v>
       </c>
       <c r="AJ113" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK113" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL113" s="3">
-        <v>45865.77083333334</v>
+        <v>45865.70833333334</v>
       </c>
     </row>
     <row r="114" spans="1:38">
@@ -14573,16 +14582,16 @@
         <v>67</v>
       </c>
       <c r="C114" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D114" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E114" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F114" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -14597,16 +14606,16 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L114">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="M114">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N114">
-        <v>7.3</v>
+        <v>3.05</v>
       </c>
       <c r="O114">
         <v>0</v>
@@ -14648,10 +14657,10 @@
         <v>0</v>
       </c>
       <c r="AB114">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="AC114">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="AD114">
         <v>0</v>
@@ -14672,10 +14681,10 @@
         <v>0</v>
       </c>
       <c r="AJ114" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK114" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL114" s="3">
         <v>45865.77083333334</v>
@@ -14692,13 +14701,13 @@
         <v>106</v>
       </c>
       <c r="D115" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E115" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F115" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -14713,7 +14722,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L115">
         <v>1.59</v>
@@ -14788,10 +14797,10 @@
         <v>0</v>
       </c>
       <c r="AJ115" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK115" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL115" s="3">
         <v>45865.77083333334</v>
@@ -14802,19 +14811,19 @@
         <v>45865</v>
       </c>
       <c r="B116" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C116" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D116" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E116" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -14829,16 +14838,16 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L116">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="M116">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N116">
-        <v>5.03</v>
+        <v>7.3</v>
       </c>
       <c r="O116">
         <v>0</v>
@@ -14880,10 +14889,10 @@
         <v>0</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD116">
         <v>0</v>
@@ -14904,13 +14913,13 @@
         <v>0</v>
       </c>
       <c r="AJ116" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK116" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL116" s="3">
-        <v>45865.79166666666</v>
+        <v>45865.77083333334</v>
       </c>
     </row>
     <row r="117" spans="1:38">
@@ -14921,16 +14930,16 @@
         <v>68</v>
       </c>
       <c r="C117" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="D117" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E117" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F117" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -14945,16 +14954,16 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L117">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M117">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="O117">
         <v>0</v>
@@ -14996,10 +15005,10 @@
         <v>0</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD117">
         <v>0</v>
@@ -15020,10 +15029,10 @@
         <v>0</v>
       </c>
       <c r="AJ117" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK117" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL117" s="3">
         <v>45865.79166666666</v>
@@ -15037,16 +15046,16 @@
         <v>68</v>
       </c>
       <c r="C118" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D118" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E118" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F118" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -15061,7 +15070,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L118">
         <v>1.62</v>
@@ -15136,10 +15145,10 @@
         <v>0</v>
       </c>
       <c r="AJ118" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK118" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL118" s="3">
         <v>45865.79166666666</v>
@@ -15150,19 +15159,19 @@
         <v>45865</v>
       </c>
       <c r="B119" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C119" t="s">
         <v>73</v>
       </c>
       <c r="D119" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E119" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F119" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -15177,7 +15186,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -15252,13 +15261,13 @@
         <v>0</v>
       </c>
       <c r="AJ119" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK119" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL119" s="3">
-        <v>45865.83333333334</v>
+        <v>45865.79166666666</v>
       </c>
     </row>
     <row r="120" spans="1:38">
@@ -15272,13 +15281,13 @@
         <v>73</v>
       </c>
       <c r="D120" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E120" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F120" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -15293,7 +15302,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L120">
         <v>0</v>
@@ -15368,10 +15377,10 @@
         <v>0</v>
       </c>
       <c r="AJ120" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK120" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL120" s="3">
         <v>45865.83333333334</v>
@@ -15382,19 +15391,19 @@
         <v>45865</v>
       </c>
       <c r="B121" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C121" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="D121" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E121" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F121" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -15409,16 +15418,16 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L121">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M121">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N121">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -15454,16 +15463,16 @@
         <v>0</v>
       </c>
       <c r="Z121">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA121">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB121">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC121">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD121">
         <v>0</v>
@@ -15484,13 +15493,13 @@
         <v>0</v>
       </c>
       <c r="AJ121" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK121" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL121" s="3">
-        <v>45865.85416666666</v>
+        <v>45865.83333333334</v>
       </c>
     </row>
     <row r="122" spans="1:38">
@@ -15498,19 +15507,19 @@
         <v>45865</v>
       </c>
       <c r="B122" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C122" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D122" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E122" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F122" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -15525,16 +15534,16 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L122">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M122">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -15570,16 +15579,16 @@
         <v>0</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD122">
         <v>0</v>
@@ -15600,13 +15609,13 @@
         <v>0</v>
       </c>
       <c r="AJ122" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK122" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL122" s="3">
-        <v>45865.89583333334</v>
+        <v>45865.85416666666</v>
       </c>
     </row>
     <row r="123" spans="1:38">
@@ -15614,19 +15623,19 @@
         <v>45865</v>
       </c>
       <c r="B123" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C123" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="D123" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E123" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F123" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -15641,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L123">
         <v>0</v>
@@ -15716,13 +15725,13 @@
         <v>0</v>
       </c>
       <c r="AJ123" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AK123" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL123" s="3">
-        <v>45865.95833333334</v>
+        <v>45865.89583333334</v>
       </c>
     </row>
     <row r="124" spans="1:38">
@@ -15736,13 +15745,13 @@
         <v>73</v>
       </c>
       <c r="D124" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E124" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F124" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -15757,7 +15766,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L124">
         <v>0</v>
@@ -15832,12 +15841,128 @@
         <v>0</v>
       </c>
       <c r="AJ124" t="s">
+        <v>361</v>
+      </c>
+      <c r="AK124" t="s">
+        <v>361</v>
+      </c>
+      <c r="AL124" s="3">
+        <v>45865.95833333334</v>
+      </c>
+    </row>
+    <row r="125" spans="1:38">
+      <c r="A125" s="2">
+        <v>45865</v>
+      </c>
+      <c r="B125" t="s">
+        <v>72</v>
+      </c>
+      <c r="C125" t="s">
+        <v>73</v>
+      </c>
+      <c r="D125" t="s">
+        <v>109</v>
+      </c>
+      <c r="E125" t="s">
+        <v>234</v>
+      </c>
+      <c r="F125" t="s">
         <v>358</v>
       </c>
-      <c r="AK124" t="s">
-        <v>358</v>
-      </c>
-      <c r="AL124" s="3">
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125" t="s">
+        <v>359</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+      <c r="Q125">
+        <v>0</v>
+      </c>
+      <c r="R125">
+        <v>0</v>
+      </c>
+      <c r="S125">
+        <v>0</v>
+      </c>
+      <c r="T125">
+        <v>0</v>
+      </c>
+      <c r="U125">
+        <v>0</v>
+      </c>
+      <c r="V125">
+        <v>0</v>
+      </c>
+      <c r="W125">
+        <v>0</v>
+      </c>
+      <c r="X125">
+        <v>0</v>
+      </c>
+      <c r="Y125">
+        <v>0</v>
+      </c>
+      <c r="Z125">
+        <v>0</v>
+      </c>
+      <c r="AA125">
+        <v>0</v>
+      </c>
+      <c r="AB125">
+        <v>0</v>
+      </c>
+      <c r="AC125">
+        <v>0</v>
+      </c>
+      <c r="AD125">
+        <v>0</v>
+      </c>
+      <c r="AE125">
+        <v>0</v>
+      </c>
+      <c r="AF125">
+        <v>0</v>
+      </c>
+      <c r="AG125">
+        <v>0</v>
+      </c>
+      <c r="AH125">
+        <v>0</v>
+      </c>
+      <c r="AI125">
+        <v>0</v>
+      </c>
+      <c r="AJ125" t="s">
+        <v>361</v>
+      </c>
+      <c r="AK125" t="s">
+        <v>361</v>
+      </c>
+      <c r="AL125" s="3">
         <v>45865.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-07-27.xlsx
+++ b/jogos_2025-07-27.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Central Coast II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.66</v>
+        <v>3.5</v>
       </c>
       <c r="M3" t="n">
         <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>1.74</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -824,58 +824,58 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Central Coast II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -956,58 +956,58 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.92</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
         <v>3.8</v>
@@ -1097,46 +1097,46 @@
         <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V5" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.8</v>
+        <v>16.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AA5" t="n">
         <v>5.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AC5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG5" t="n">
         <v>2.6</v>
       </c>
-      <c r="AD5" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AH5" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AI5" t="n">
         <v>1.29</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="M8" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>3.67</v>
+        <v>2.86</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.29</v>
+        <v>1.67</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.01</v>
+        <v>3.87</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.67</v>
+        <v>2.57</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.87</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>1.54</v>
+        <v>2.09</v>
       </c>
       <c r="P10" t="n">
-        <v>15.25</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.49</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.52</v>
+        <v>3.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.45</v>
+        <v>7</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,73 +1862,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.57</v>
+        <v>2.21</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>3.08</v>
       </c>
       <c r="O11" t="n">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="P11" t="n">
-        <v>9.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.42</v>
+        <v>4.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AH11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AI11" t="n">
         <v>1.04</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="P12" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD12" t="n">
         <v>2.62</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.14</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.35</v>
+        <v>4.8</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.36</v>
+        <v>3.29</v>
       </c>
       <c r="M13" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="O13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.21</v>
+        <v>3.36</v>
       </c>
       <c r="M15" t="n">
-        <v>2.92</v>
+        <v>3.27</v>
       </c>
       <c r="N15" t="n">
-        <v>3.08</v>
+        <v>1.93</v>
       </c>
       <c r="O15" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="P15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH15" t="n">
         <v>6.5</v>
       </c>
-      <c r="Q15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="AI15" t="n">
         <v>1.1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.04</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,37 +2786,37 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.9</v>
+        <v>1.25</v>
       </c>
       <c r="M18" t="n">
+        <v>6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q18" t="n">
         <v>3.35</v>
       </c>
-      <c r="N18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P18" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.83</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="W18" t="n">
         <v>1.1</v>
@@ -2825,37 +2825,37 @@
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.44</v>
+        <v>5.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AC18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH18" t="n">
-        <v>6.4</v>
+        <v>4.33</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,37 +3050,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.25</v>
+        <v>2.9</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>2.33</v>
       </c>
       <c r="O20" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
         <v>1.1</v>
@@ -3089,37 +3089,37 @@
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.25</v>
+        <v>3.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.93</v>
+        <v>3.15</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.76</v>
+        <v>1.27</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.33</v>
+        <v>6.4</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.33</v>
+        <v>2.75</v>
       </c>
       <c r="M27" t="n">
-        <v>5.8</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>6.8</v>
+        <v>2.17</v>
       </c>
       <c r="O27" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="P27" t="n">
-        <v>38</v>
+        <v>14.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="R27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z27" t="n">
         <v>1.17</v>
       </c>
-      <c r="S27" t="n">
+      <c r="AA27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH27" t="n">
         <v>5</v>
       </c>
-      <c r="T27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AI27" t="n">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="N28" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="S28" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="V28" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.5</v>
+        <v>7.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.89</v>
+        <v>1.29</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.81</v>
+        <v>3.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.45</v>
+        <v>1.62</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.3</v>
+        <v>2.12</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AH28" t="n">
-        <v>6.5</v>
+        <v>2.39</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.11</v>
+        <v>1.46</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>3.99</v>
       </c>
       <c r="N29" t="n">
-        <v>2.76</v>
+        <v>5.5</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.11</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>8</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA30" t="n">
         <v>3.5</v>
       </c>
-      <c r="N30" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,73 +4502,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.92</v>
+        <v>2.01</v>
       </c>
       <c r="M31" t="n">
-        <v>3.39</v>
+        <v>3.65</v>
       </c>
       <c r="N31" t="n">
-        <v>2.08</v>
+        <v>3.42</v>
       </c>
       <c r="O31" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="P31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="W31" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
         <v>11</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AA31" t="n">
         <v>4.33</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC31" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="AE31" t="n">
         <v>1.48</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG31" t="n">
         <v>2.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>5</v>
+        <v>4.63</v>
       </c>
       <c r="AI31" t="n">
         <v>1.18</v>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF32" t="n">
         <v>1.57</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="N32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AG32" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>5.95</v>
+        <v>5</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="M34" t="n">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="M36" t="n">
-        <v>3.93</v>
+        <v>4.2</v>
       </c>
       <c r="N36" t="n">
-        <v>5.1</v>
+        <v>6.57</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="N40" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA41" t="n">
         <v>4.2</v>
       </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
       <c r="AB41" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AD41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG41" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.56</v>
+        <v>3.16</v>
       </c>
       <c r="M42" t="n">
-        <v>3.96</v>
+        <v>3.08</v>
       </c>
       <c r="N42" t="n">
-        <v>4.4</v>
+        <v>2.25</v>
       </c>
       <c r="O42" t="n">
-        <v>1.3</v>
+        <v>2.41</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.55</v>
+        <v>2.49</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AG42" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,22 +6086,22 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.7</v>
+        <v>2.85</v>
       </c>
       <c r="M43" t="n">
-        <v>3.83</v>
+        <v>3.2</v>
       </c>
       <c r="N43" t="n">
-        <v>3.71</v>
+        <v>2.29</v>
       </c>
       <c r="O43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6146,10 +6146,10 @@
         <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
         <v>0</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,76 +6218,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.09</v>
+        <v>1.5</v>
       </c>
       <c r="M44" t="n">
-        <v>3.11</v>
+        <v>3.9</v>
       </c>
       <c r="N44" t="n">
-        <v>3.14</v>
+        <v>4.93</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,64 +6350,64 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4</v>
+      </c>
+      <c r="N45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE45" t="n">
         <v>1.61</v>
-      </c>
-      <c r="M45" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N45" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,76 +6482,76 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.28</v>
+        <v>1.7</v>
       </c>
       <c r="M46" t="n">
-        <v>3.08</v>
+        <v>3.97</v>
       </c>
       <c r="N46" t="n">
-        <v>2.32</v>
+        <v>4.66</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,40 +6614,40 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.71</v>
+        <v>2.09</v>
       </c>
       <c r="M47" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.3</v>
+        <v>3.23</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -6662,11 +6662,11 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC47" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC47" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AD47" t="n">
         <v>0</v>
       </c>
@@ -6674,10 +6674,10 @@
         <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>4.1</v>
+        <v>1.53</v>
       </c>
       <c r="M48" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="N48" t="n">
-        <v>1.62</v>
+        <v>4.75</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,16 +6794,16 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.53</v>
+        <v>4.1</v>
       </c>
       <c r="M49" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="N49" t="n">
-        <v>4.75</v>
+        <v>1.62</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,16 +6926,16 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
         <v>0</v>
@@ -7019,43 +7019,43 @@
         <v>2.87</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AB50" t="n">
         <v>1.9</v>
@@ -7064,22 +7064,22 @@
         <v>1.9</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,76 +7274,76 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.27</v>
+        <v>1.68</v>
       </c>
       <c r="M52" t="n">
-        <v>3.38</v>
+        <v>3.02</v>
       </c>
       <c r="N52" t="n">
-        <v>1.93</v>
+        <v>3.79</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -7370,22 +7370,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,76 +7406,76 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,76 +7802,76 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.18</v>
+        <v>1.51</v>
       </c>
       <c r="M56" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="N56" t="n">
-        <v>2.95</v>
+        <v>5.7</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.75</v>
+        <v>2.19</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,76 +7934,76 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="M59" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="N59" t="n">
-        <v>3.34</v>
+        <v>3.67</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,76 +8330,76 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N60" t="n">
-        <v>3.67</v>
+        <v>3.34</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI60" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -8471,31 +8471,31 @@
         <v>6.9</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
@@ -8522,10 +8522,10 @@
         <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH61" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M62" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="N62" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8612,58 +8612,58 @@
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.62</v>
+        <v>2.59</v>
       </c>
       <c r="M63" t="n">
-        <v>3.54</v>
+        <v>3.41</v>
       </c>
       <c r="N63" t="n">
-        <v>6.2</v>
+        <v>2.27</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8744,58 +8744,58 @@
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA63" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>2.47</v>
-      </c>
       <c r="AC63" t="n">
-        <v>1.43</v>
+        <v>2.35</v>
       </c>
       <c r="AD63" t="n">
-        <v>5.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AF63" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.59</v>
+        <v>1.61</v>
       </c>
       <c r="M64" t="n">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="N64" t="n">
-        <v>2.27</v>
+        <v>5.2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,16 +8906,16 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AD64" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
         <v>0</v>
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9350,22 +9350,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="M70" t="n">
         <v>3.2</v>
       </c>
       <c r="N70" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>3.97</v>
       </c>
       <c r="N71" t="n">
-        <v>2.95</v>
+        <v>1.61</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>5.1</v>
+        <v>2.53</v>
       </c>
       <c r="M72" t="n">
-        <v>3.97</v>
+        <v>3.27</v>
       </c>
       <c r="N72" t="n">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.27</v>
+        <v>1.51</v>
       </c>
       <c r="M73" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N73" t="n">
-        <v>2.81</v>
+        <v>5.2</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10184,7 +10184,7 @@
         <v>4</v>
       </c>
       <c r="N74" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="M75" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.53</v>
+        <v>2.27</v>
       </c>
       <c r="M76" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="N76" t="n">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="M77" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N77" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.51</v>
+        <v>2.38</v>
       </c>
       <c r="M78" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N78" t="n">
-        <v>4.8</v>
+        <v>2.63</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10757,7 +10757,7 @@
         <v>1.8</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="M82" t="n">
-        <v>3.18</v>
+        <v>2.6</v>
       </c>
       <c r="N82" t="n">
-        <v>2.39</v>
+        <v>2.89</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11494,17 +11494,17 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="M84" t="n">
-        <v>2.95</v>
+        <v>2.56</v>
       </c>
       <c r="N84" t="n">
-        <v>2.31</v>
+        <v>4.3</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11540,10 +11540,10 @@
         <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,22 +11726,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11758,17 +11758,17 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11804,10 +11804,10 @@
         <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12550,17 +12550,17 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.69</v>
+        <v>1.93</v>
       </c>
       <c r="M92" t="n">
-        <v>2.38</v>
+        <v>2.79</v>
       </c>
       <c r="N92" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12596,10 +12596,10 @@
         <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB92" t="n">
         <v>0</v>
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12682,17 +12682,17 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.93</v>
+        <v>3.26</v>
       </c>
       <c r="M93" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="N93" t="n">
-        <v>4.1</v>
+        <v>2.16</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12728,10 +12728,10 @@
         <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB93" t="n">
         <v>0</v>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.26</v>
+        <v>2.69</v>
       </c>
       <c r="M95" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="N95" t="n">
-        <v>2.16</v>
+        <v>3.05</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12992,10 +12992,10 @@
         <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AB95" t="n">
         <v>0</v>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="M97" t="n">
-        <v>2.66</v>
+        <v>4</v>
       </c>
       <c r="N97" t="n">
-        <v>4.5</v>
+        <v>7.3</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13256,16 +13256,16 @@
         <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,22 +13442,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.99</v>
+        <v>1.93</v>
       </c>
       <c r="M99" t="n">
-        <v>3.38</v>
+        <v>2.66</v>
       </c>
       <c r="N99" t="n">
-        <v>2.04</v>
+        <v>4.5</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13520,10 +13520,10 @@
         <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB99" t="n">
         <v>0</v>
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.15</v>
+        <v>2.99</v>
       </c>
       <c r="M102" t="n">
-        <v>3.03</v>
+        <v>3.38</v>
       </c>
       <c r="N102" t="n">
-        <v>3.08</v>
+        <v>2.04</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13916,16 +13916,16 @@
         <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14048,16 +14048,16 @@
         <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14180,16 +14180,16 @@
         <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14324,10 +14324,10 @@
         <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF105" t="n">
         <v>0</v>
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         <v>0</v>
       </c>
       <c r="AD106" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
         <v>0</v>
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.66</v>
+        <v>3.6</v>
       </c>
       <c r="M107" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N107" t="n">
-        <v>4</v>
+        <v>1.76</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14588,10 +14588,10 @@
         <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AF107" t="n">
         <v>0</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC118" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M119" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N119" t="n">
-        <v>5.25</v>
+        <v>5.03</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>2.28</v>
       </c>
       <c r="AC119" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G125" t="n">

--- a/jogos_2025-07-27.xlsx
+++ b/jogos_2025-07-27.xlsx
@@ -692,10 +692,10 @@
         <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="T2" t="n">
         <v>2.33</v>
@@ -722,13 +722,13 @@
         <v>4.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AE2" t="n">
         <v>1.44</v>
@@ -740,7 +740,7 @@
         <v>2.32</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AI2" t="n">
         <v>1.15</v>
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Central Coast II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="N3" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,25 +938,25 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="N4" t="n">
-        <v>1.92</v>
+        <v>3.38</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
         <v>3.8</v>
@@ -965,46 +965,46 @@
         <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V4" t="n">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.8</v>
+        <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AA4" t="n">
         <v>5.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AC4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG4" t="n">
         <v>2.6</v>
       </c>
-      <c r="AD4" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AH4" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AI4" t="n">
         <v>1.29</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Central Coast II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.66</v>
+        <v>2.82</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="N5" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1088,58 +1088,58 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>3.87</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>15.25</v>
+        <v>12.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.49</v>
+        <v>4.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.52</v>
+        <v>3.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.45</v>
+        <v>6.35</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.21</v>
+        <v>1.67</v>
       </c>
       <c r="M11" t="n">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>3.08</v>
+        <v>3.87</v>
       </c>
       <c r="O11" t="n">
-        <v>1.98</v>
+        <v>1.54</v>
       </c>
       <c r="P11" t="n">
-        <v>6.5</v>
+        <v>15.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="R11" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.5</v>
+        <v>4.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.6</v>
+        <v>2.52</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>10</v>
+        <v>4.45</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.29</v>
+        <v>2.21</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="N13" t="n">
-        <v>2.01</v>
+        <v>3.08</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2267,43 +2267,43 @@
         <v>1.91</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
         <v>2.1</v>
@@ -2312,22 +2312,22 @@
         <v>1.61</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>3.29</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P16" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V16" t="n">
         <v>8</v>
       </c>
-      <c r="O16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="W16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA16" t="n">
         <v>3</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="AB16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.06</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,37 +2786,37 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.25</v>
+        <v>2.94</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>3.52</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>2.32</v>
       </c>
       <c r="O18" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>12.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>1.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
         <v>1.1</v>
@@ -2825,37 +2825,37 @@
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.25</v>
+        <v>3.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.93</v>
+        <v>3.04</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.76</v>
+        <v>1.29</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,37 +3050,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.9</v>
+        <v>1.25</v>
       </c>
       <c r="M20" t="n">
+        <v>6</v>
+      </c>
+      <c r="N20" t="n">
+        <v>9</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3.35</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P20" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.83</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="W20" t="n">
         <v>1.1</v>
@@ -3089,37 +3089,37 @@
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.44</v>
+        <v>5.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AC20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH20" t="n">
-        <v>6.4</v>
+        <v>4.33</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.75</v>
+        <v>2.01</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>2.17</v>
+        <v>3.42</v>
       </c>
       <c r="O27" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="P27" t="n">
-        <v>14.75</v>
+        <v>11.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
-        <v>5.65</v>
+        <v>5.25</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>5</v>
+        <v>4.63</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.01</v>
+        <v>2.75</v>
       </c>
       <c r="M31" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="N31" t="n">
-        <v>3.42</v>
+        <v>2.17</v>
       </c>
       <c r="O31" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="P31" t="n">
-        <v>11.5</v>
+        <v>14.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="U31" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>5.25</v>
+        <v>5.65</v>
       </c>
       <c r="W31" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.63</v>
+        <v>5</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="N34" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="O34" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="P34" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V34" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="W34" t="n">
         <v>1.1</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AD34" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG34" t="n">
         <v>2.05</v>
       </c>
       <c r="AH34" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="M35" t="n">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="O35" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="P35" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U35" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="V35" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="W35" t="n">
         <v>1.1</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG35" t="n">
         <v>2.05</v>
       </c>
       <c r="AH35" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.42</v>
+        <v>2.19</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6</v>
+        <v>3.53</v>
       </c>
       <c r="N38" t="n">
-        <v>6.95</v>
+        <v>2.62</v>
       </c>
       <c r="O38" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="P38" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="U38" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V38" t="n">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="W38" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.19</v>
+        <v>1.42</v>
       </c>
       <c r="M39" t="n">
-        <v>3.53</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>2.62</v>
+        <v>6.95</v>
       </c>
       <c r="O39" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="P39" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T39" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="U39" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V39" t="n">
-        <v>5.75</v>
+        <v>5.45</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="AD39" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH39" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,64 +5690,64 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="M40" t="n">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="O40" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="P40" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R40" t="n">
         <v>1.36</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T40" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U40" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V40" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="W40" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X40" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y40" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD40" t="n">
         <v>3.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF40" t="n">
         <v>1.67</v>
@@ -5756,7 +5756,7 @@
         <v>2.1</v>
       </c>
       <c r="AH40" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AI40" t="n">
         <v>1.11</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.85</v>
+        <v>1.66</v>
       </c>
       <c r="M43" t="n">
-        <v>3.2</v>
+        <v>4.28</v>
       </c>
       <c r="N43" t="n">
-        <v>2.29</v>
+        <v>4.1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.85</v>
+        <v>2.57</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,76 +6218,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.5</v>
+        <v>2.09</v>
       </c>
       <c r="M44" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>4.93</v>
+        <v>3.23</v>
       </c>
       <c r="O44" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="P44" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="R44" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S44" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="T44" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="U44" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V44" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="W44" t="n">
         <v>1.08</v>
       </c>
       <c r="X44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH44" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="N45" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P45" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V45" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA45" t="n">
         <v>4.2</v>
       </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
       <c r="AB45" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,76 +6482,76 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.97</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="n">
-        <v>4.66</v>
+        <v>4.93</v>
       </c>
       <c r="O46" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="P46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="R46" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S46" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T46" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="U46" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="V46" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X46" t="n">
         <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AF46" t="n">
         <v>1.65</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH46" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.09</v>
+        <v>2.71</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="N47" t="n">
-        <v>3.23</v>
+        <v>2.3</v>
       </c>
       <c r="O47" t="n">
+        <v>2</v>
+      </c>
+      <c r="P47" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V47" t="n">
+        <v>7</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF47" t="n">
         <v>1.67</v>
       </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V47" t="n">
-        <v>8</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG47" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="M48" t="n">
-        <v>3.92</v>
+        <v>3.33</v>
       </c>
       <c r="N48" t="n">
-        <v>4.75</v>
+        <v>2.87</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.28</v>
+        <v>4.05</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>4.1</v>
+        <v>1.53</v>
       </c>
       <c r="M49" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="N49" t="n">
-        <v>1.62</v>
+        <v>4.75</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.38</v>
+        <v>4.1</v>
       </c>
       <c r="M50" t="n">
-        <v>3.33</v>
+        <v>3.88</v>
       </c>
       <c r="N50" t="n">
-        <v>2.87</v>
+        <v>1.62</v>
       </c>
       <c r="O50" t="n">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="P50" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="R50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U50" t="n">
         <v>1.44</v>
       </c>
-      <c r="S50" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.32</v>
-      </c>
       <c r="V50" t="n">
-        <v>8.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y50" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.94</v>
+        <v>3.95</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD50" t="n">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="n">
-        <v>8.199999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,76 +7274,76 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="M52" t="n">
-        <v>3.02</v>
+        <v>4.4</v>
       </c>
       <c r="N52" t="n">
-        <v>3.79</v>
+        <v>5.7</v>
       </c>
       <c r="O52" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P52" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V52" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB52" t="n">
         <v>1.65</v>
       </c>
-      <c r="P52" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S52" t="n">
+      <c r="AC52" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD52" t="n">
         <v>2.53</v>
       </c>
-      <c r="T52" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V52" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1</v>
-      </c>
-      <c r="X52" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>4.25</v>
-      </c>
       <c r="AE52" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="n">
-        <v>9</v>
+        <v>4.65</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,76 +7670,76 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -7766,22 +7766,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,76 +7802,76 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>16.25</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,76 +8066,76 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,76 +8330,76 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.91</v>
+        <v>1.38</v>
       </c>
       <c r="M60" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>3.34</v>
+        <v>6.9</v>
       </c>
       <c r="O60" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="P60" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="R60" t="n">
         <v>1.36</v>
       </c>
       <c r="S60" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T60" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U60" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V60" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="W60" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X60" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AD60" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AG60" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AH60" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,76 +8462,76 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="N61" t="n">
-        <v>6.9</v>
+        <v>3.34</v>
       </c>
       <c r="O61" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="R61" t="n">
         <v>1.36</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T61" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U61" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V61" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W61" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF61" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AG61" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI61" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.62</v>
+        <v>2.59</v>
       </c>
       <c r="M62" t="n">
-        <v>3.54</v>
+        <v>3.41</v>
       </c>
       <c r="N62" t="n">
-        <v>6.2</v>
+        <v>2.27</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8612,58 +8612,58 @@
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA62" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>2.47</v>
-      </c>
       <c r="AC62" t="n">
-        <v>1.43</v>
+        <v>2.35</v>
       </c>
       <c r="AD62" t="n">
-        <v>5.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AF62" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
       <c r="M63" t="n">
-        <v>3.41</v>
+        <v>3.64</v>
       </c>
       <c r="N63" t="n">
-        <v>2.27</v>
+        <v>2.92</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8780,10 +8780,10 @@
         <v>2.35</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AF63" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,76 +8990,76 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="M65" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="N65" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T65" t="n">
         <v>3.64</v>
       </c>
-      <c r="N65" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.53</v>
+        <v>2.47</v>
       </c>
       <c r="AC65" t="n">
-        <v>2.35</v>
+        <v>1.43</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.55</v>
+        <v>5.05</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.49</v>
+        <v>1.1</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI65" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,22 +9350,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="M68" t="n">
-        <v>3.61</v>
+        <v>3.15</v>
       </c>
       <c r="N68" t="n">
-        <v>3.91</v>
+        <v>2.67</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="M70" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC70" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.1</v>
+        <v>2.38</v>
       </c>
       <c r="M71" t="n">
-        <v>3.97</v>
+        <v>3.2</v>
       </c>
       <c r="N71" t="n">
-        <v>1.61</v>
+        <v>2.63</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.53</v>
+        <v>2.27</v>
       </c>
       <c r="M72" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="N72" t="n">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.51</v>
+        <v>2.32</v>
       </c>
       <c r="M74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N74" t="n">
-        <v>4.8</v>
+        <v>2.95</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="M75" t="n">
-        <v>3</v>
+        <v>3.97</v>
       </c>
       <c r="N75" t="n">
-        <v>2.95</v>
+        <v>1.61</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.27</v>
+        <v>2.53</v>
       </c>
       <c r="M76" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="N76" t="n">
-        <v>2.81</v>
+        <v>2.38</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.27</v>
+        <v>1.51</v>
       </c>
       <c r="M77" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N77" t="n">
-        <v>2.81</v>
+        <v>4.8</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10625,7 +10625,7 @@
         <v>1.8</v>
       </c>
       <c r="AC77" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="M78" t="n">
         <v>3.2</v>
       </c>
       <c r="N78" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.84</v>
+        <v>3.05</v>
       </c>
       <c r="M83" t="n">
-        <v>3.37</v>
+        <v>2.95</v>
       </c>
       <c r="N83" t="n">
-        <v>3.57</v>
+        <v>2.31</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.05</v>
+        <v>2.57</v>
       </c>
       <c r="M87" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="N87" t="n">
-        <v>2.31</v>
+        <v>2.89</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.52</v>
+        <v>1.35</v>
       </c>
       <c r="M88" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N88" t="n">
-        <v>1.86</v>
+        <v>7.2</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,16 +12074,16 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.35</v>
+        <v>3.52</v>
       </c>
       <c r="M89" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="N89" t="n">
-        <v>7.2</v>
+        <v>1.86</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,16 +12206,16 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD89" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
         <v>0</v>
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.55</v>
+        <v>3.26</v>
       </c>
       <c r="M91" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="N91" t="n">
-        <v>2.9</v>
+        <v>2.16</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12464,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB91" t="n">
         <v>0</v>
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12550,17 +12550,17 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="M92" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="N92" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12596,10 +12596,10 @@
         <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
         <v>0</v>
@@ -12650,22 +12650,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.26</v>
+        <v>2.59</v>
       </c>
       <c r="M93" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N93" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12728,16 +12728,16 @@
         <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,22 +12782,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12814,17 +12814,17 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.59</v>
+        <v>1.93</v>
       </c>
       <c r="M94" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="N94" t="n">
-        <v>2.58</v>
+        <v>4.1</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12860,16 +12860,16 @@
         <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AB94" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="M97" t="n">
-        <v>4</v>
+        <v>3.03</v>
       </c>
       <c r="N97" t="n">
-        <v>7.3</v>
+        <v>3.08</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13256,16 +13256,16 @@
         <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AA97" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="AB97" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13388,10 +13388,10 @@
         <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13520,10 +13520,10 @@
         <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
         <v>0</v>
@@ -13574,22 +13574,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.46</v>
+        <v>2.99</v>
       </c>
       <c r="M100" t="n">
-        <v>3.85</v>
+        <v>3.38</v>
       </c>
       <c r="N100" t="n">
-        <v>7</v>
+        <v>2.04</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.99</v>
+        <v>1.46</v>
       </c>
       <c r="M102" t="n">
-        <v>3.38</v>
+        <v>3.85</v>
       </c>
       <c r="N102" t="n">
-        <v>2.04</v>
+        <v>7</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="M104" t="n">
-        <v>3.03</v>
+        <v>4</v>
       </c>
       <c r="N104" t="n">
-        <v>3.08</v>
+        <v>7.3</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14180,16 +14180,16 @@
         <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.66</v>
+        <v>3.6</v>
       </c>
       <c r="M105" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N105" t="n">
-        <v>4</v>
+        <v>1.76</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14324,10 +14324,10 @@
         <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AF105" t="n">
         <v>0</v>
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         <v>0</v>
       </c>
       <c r="AD106" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF106" t="n">
         <v>0</v>
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14588,10 +14588,10 @@
         <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
         <v>0</v>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14794,17 +14794,17 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.31</v>
+        <v>1.78</v>
       </c>
       <c r="M109" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="N109" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14926,17 +14926,17 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="M110" t="n">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="N110" t="n">
-        <v>5.5</v>
+        <v>4.84</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14978,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC110" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD110" t="n">
         <v>0</v>
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.69</v>
+        <v>2.31</v>
       </c>
       <c r="M112" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="N112" t="n">
-        <v>4.84</v>
+        <v>3.1</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15242,10 +15242,10 @@
         <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M118" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N118" t="n">
-        <v>5.25</v>
+        <v>5.03</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16037,7 +16037,7 @@
         <v>2.28</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="M119" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N119" t="n">
-        <v>5.03</v>
+        <v>5.25</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>2.28</v>
       </c>
       <c r="AC119" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G121" t="n">

--- a/jogos_2025-07-27.xlsx
+++ b/jogos_2025-07-27.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,73 +806,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.92</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.52</v>
+        <v>3.82</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>3.38</v>
       </c>
       <c r="O3" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>20.5</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
         <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V3" t="n">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>14.8</v>
+        <v>16.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AA3" t="n">
         <v>5.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AC3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG3" t="n">
         <v>2.6</v>
       </c>
-      <c r="AD3" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.67</v>
-      </c>
       <c r="AH3" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AI3" t="n">
         <v>1.29</v>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,73 +938,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>2.92</v>
       </c>
       <c r="M4" t="n">
-        <v>3.82</v>
+        <v>3.52</v>
       </c>
       <c r="N4" t="n">
-        <v>3.38</v>
+        <v>1.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="P4" t="n">
-        <v>23</v>
+        <v>20.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
         <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V4" t="n">
-        <v>4.25</v>
+        <v>4.55</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>14.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AA4" t="n">
         <v>5.5</v>
       </c>
       <c r="AB4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.42</v>
       </c>
-      <c r="AC4" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AG4" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="AI4" t="n">
         <v>1.29</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.28</v>
+        <v>2.57</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="P9" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V9" t="n">
         <v>8</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V9" t="n">
-        <v>7</v>
       </c>
       <c r="W9" t="n">
         <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.35</v>
+        <v>7</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.57</v>
+        <v>2.21</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>3.08</v>
       </c>
       <c r="O10" t="n">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="P10" t="n">
-        <v>9.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.42</v>
+        <v>4.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AH10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AI10" t="n">
         <v>1.04</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.67</v>
+        <v>3.29</v>
       </c>
       <c r="M11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD11" t="n">
         <v>3.8</v>
       </c>
-      <c r="N11" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P11" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.52</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.45</v>
+        <v>7.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.45</v>
+        <v>3.64</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>1.91</v>
       </c>
       <c r="O12" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="P12" t="n">
-        <v>9</v>
+        <v>8.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>1.72</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.86</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AF12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.8</v>
       </c>
-      <c r="AG12" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH12" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.21</v>
+        <v>3.36</v>
       </c>
       <c r="M13" t="n">
-        <v>2.92</v>
+        <v>3.27</v>
       </c>
       <c r="N13" t="n">
-        <v>3.08</v>
+        <v>1.93</v>
       </c>
       <c r="O13" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="P13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH13" t="n">
         <v>6.5</v>
       </c>
-      <c r="Q13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="AI13" t="n">
         <v>1.1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.04</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.64</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>1.91</v>
+        <v>3.87</v>
       </c>
       <c r="O14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P14" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.4</v>
       </c>
-      <c r="P14" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC14" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AD14" t="n">
-        <v>3.8</v>
+        <v>2.52</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>7.5</v>
+        <v>4.45</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,52 +2390,52 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.36</v>
+        <v>1.28</v>
       </c>
       <c r="M15" t="n">
-        <v>3.27</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>1.93</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.45</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.75</v>
+        <v>4.33</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>6.45</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AB15" t="n">
         <v>1.88</v>
@@ -2444,22 +2444,22 @@
         <v>1.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AH15" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.29</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.01</v>
+        <v>5.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.37</v>
+        <v>1.44</v>
       </c>
       <c r="P16" t="n">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>3</v>
+        <v>3.86</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,22 +2786,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="O18" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="P18" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
         <v>1.36</v>
@@ -2810,10 +2810,10 @@
         <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
         <v>7</v>
@@ -2834,16 +2834,16 @@
         <v>3.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AF18" t="n">
         <v>1.7</v>
@@ -2852,10 +2852,10 @@
         <v>2.05</v>
       </c>
       <c r="AH18" t="n">
-        <v>5.75</v>
+        <v>6.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,37 +3050,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.25</v>
+        <v>2.94</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>3.52</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>2.32</v>
       </c>
       <c r="O20" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>17</v>
+        <v>12.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>1.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
         <v>1.1</v>
@@ -3089,37 +3089,37 @@
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.25</v>
+        <v>3.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.93</v>
+        <v>3.04</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.76</v>
+        <v>1.29</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,22 +3710,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="P25" t="n">
-        <v>21</v>
+        <v>16.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
         <v>1.25</v>
@@ -3734,16 +3734,16 @@
         <v>3.75</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U25" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
@@ -3752,34 +3752,34 @@
         <v>17</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AA25" t="n">
-        <v>5.55</v>
+        <v>4.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,22 +3842,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="M26" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>16.25</v>
+        <v>21</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R26" t="n">
         <v>1.25</v>
@@ -3866,16 +3866,16 @@
         <v>3.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
@@ -3884,34 +3884,34 @@
         <v>17</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.4</v>
+        <v>5.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.99</v>
       </c>
       <c r="N27" t="n">
-        <v>3.42</v>
+        <v>5.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="P27" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="T27" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>5.25</v>
+        <v>6.8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.53</v>
+        <v>3.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.25</v>
+        <v>1.79</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.63</v>
+        <v>5.95</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.33</v>
+        <v>2.92</v>
       </c>
       <c r="M28" t="n">
-        <v>5.8</v>
+        <v>3.39</v>
       </c>
       <c r="N28" t="n">
-        <v>6.8</v>
+        <v>2.08</v>
       </c>
       <c r="O28" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="P28" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="R28" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH28" t="n">
         <v>5</v>
       </c>
-      <c r="T28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AI28" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P29" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF29" t="n">
         <v>1.57</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V29" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AG29" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>5.95</v>
+        <v>5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="M31" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.17</v>
+        <v>6.8</v>
       </c>
       <c r="O31" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="P31" t="n">
-        <v>14.75</v>
+        <v>38</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.46</v>
+        <v>1.8</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="V31" t="n">
-        <v>5.65</v>
+        <v>3.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.13</v>
+        <v>3.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.42</v>
+        <v>2.12</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH31" t="n">
-        <v>5</v>
+        <v>2.39</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,73 +4634,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.92</v>
+        <v>2.01</v>
       </c>
       <c r="M32" t="n">
-        <v>3.39</v>
+        <v>3.65</v>
       </c>
       <c r="N32" t="n">
-        <v>2.08</v>
+        <v>3.42</v>
       </c>
       <c r="O32" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="P32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S32" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U32" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="W32" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X32" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
         <v>11</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AA32" t="n">
         <v>4.33</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC32" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="AE32" t="n">
         <v>1.48</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG32" t="n">
         <v>2.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>5</v>
+        <v>4.63</v>
       </c>
       <c r="AI32" t="n">
         <v>1.18</v>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.82</v>
+        <v>1.71</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>3.9</v>
       </c>
       <c r="O33" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="P33" t="n">
         <v>10</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="R33" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="U33" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="V33" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>3.82</v>
       </c>
       <c r="M34" t="n">
-        <v>3.26</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="P34" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T34" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V34" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="N35" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="O35" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="P35" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V35" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="W35" t="n">
         <v>1.1</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AD35" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG35" t="n">
         <v>2.05</v>
       </c>
       <c r="AH35" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.73</v>
+        <v>2.19</v>
       </c>
       <c r="M37" t="n">
-        <v>3.63</v>
+        <v>3.53</v>
       </c>
       <c r="N37" t="n">
-        <v>3.78</v>
+        <v>2.62</v>
       </c>
       <c r="O37" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="P37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="n">
         <v>2.45</v>
       </c>
-      <c r="R37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.35</v>
-      </c>
       <c r="U37" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="V37" t="n">
-        <v>5.15</v>
+        <v>5.75</v>
       </c>
       <c r="W37" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AB37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF37" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AG37" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH37" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.19</v>
+        <v>1.73</v>
       </c>
       <c r="M38" t="n">
-        <v>3.53</v>
+        <v>3.63</v>
       </c>
       <c r="N38" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P38" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V38" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD38" t="n">
         <v>2.62</v>
       </c>
-      <c r="O38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P38" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V38" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>3</v>
-      </c>
       <c r="AE38" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.7</v>
+        <v>2.09</v>
       </c>
       <c r="M40" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.41</v>
+        <v>3.23</v>
       </c>
       <c r="O40" t="n">
-        <v>2.11</v>
+        <v>1.67</v>
       </c>
       <c r="P40" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="R40" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V40" t="n">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="W40" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,73 +5822,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.75</v>
+        <v>2.71</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>3.17</v>
       </c>
       <c r="N41" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="O41" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S41" t="n">
         <v>3</v>
       </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V41" t="n">
+        <v>7</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z41" t="n">
         <v>1.3</v>
       </c>
-      <c r="S41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AA41" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF41" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.65</v>
       </c>
       <c r="AG41" t="n">
         <v>2.1</v>
       </c>
       <c r="AH41" t="n">
-        <v>4.4</v>
+        <v>6.25</v>
       </c>
       <c r="AI41" t="n">
         <v>1.11</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.16</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="O42" t="n">
-        <v>2.41</v>
+        <v>1.4</v>
       </c>
       <c r="P42" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="S42" t="n">
-        <v>2.41</v>
+        <v>3.2</v>
       </c>
       <c r="T42" t="n">
-        <v>3.56</v>
+        <v>2.4</v>
       </c>
       <c r="U42" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="V42" t="n">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="X42" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
-        <v>6.7</v>
+        <v>11.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.49</v>
+        <v>1.67</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.46</v>
+        <v>2.1</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AH42" t="n">
-        <v>12</v>
+        <v>4.4</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="M43" t="n">
-        <v>4.28</v>
+        <v>3.97</v>
       </c>
       <c r="N43" t="n">
-        <v>4.1</v>
+        <v>4.66</v>
       </c>
       <c r="O43" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="P43" t="n">
-        <v>20.5</v>
+        <v>12</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S43" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T43" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="U43" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="V43" t="n">
-        <v>4.7</v>
+        <v>5.95</v>
       </c>
       <c r="W43" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y43" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AB43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE43" t="n">
         <v>1.46</v>
       </c>
-      <c r="AC43" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AF43" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>3.64</v>
+        <v>4.8</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,76 +6218,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.09</v>
+        <v>2.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N44" t="n">
-        <v>3.23</v>
+        <v>2.41</v>
       </c>
       <c r="O44" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P44" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V44" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF44" t="n">
         <v>1.67</v>
       </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V44" t="n">
-        <v>8</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG44" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.97</v>
+        <v>3.9</v>
       </c>
       <c r="N45" t="n">
-        <v>4.66</v>
+        <v>4.93</v>
       </c>
       <c r="O45" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="P45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="R45" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S45" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T45" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="U45" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="V45" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X45" t="n">
         <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AF45" t="n">
         <v>1.65</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,76 +6482,76 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="M46" t="n">
-        <v>3.9</v>
+        <v>4.28</v>
       </c>
       <c r="N46" t="n">
-        <v>4.93</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="P46" t="n">
-        <v>11</v>
+        <v>20.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="R46" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T46" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="U46" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V46" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF46" t="n">
         <v>1.55</v>
       </c>
-      <c r="V46" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG46" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AH46" t="n">
-        <v>4.3</v>
+        <v>3.64</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.71</v>
+        <v>3.16</v>
       </c>
       <c r="M47" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="N47" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="P47" t="n">
-        <v>9.5</v>
+        <v>6.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="R47" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="T47" t="n">
-        <v>2.63</v>
+        <v>3.56</v>
       </c>
       <c r="U47" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V47" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="W47" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y47" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.8</v>
+        <v>2.49</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.67</v>
+        <v>2.07</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="AH47" t="n">
-        <v>6.25</v>
+        <v>12</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="M48" t="n">
-        <v>3.33</v>
+        <v>3.92</v>
       </c>
       <c r="N48" t="n">
-        <v>2.87</v>
+        <v>4.75</v>
       </c>
       <c r="O48" t="n">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="P48" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="R48" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S48" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="T48" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="U48" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="V48" t="n">
-        <v>8.699999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="W48" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y48" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.94</v>
+        <v>4.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AD48" t="n">
-        <v>4.05</v>
+        <v>2.28</v>
       </c>
       <c r="AE48" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AI48" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>1.02</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.53</v>
+        <v>4.1</v>
       </c>
       <c r="M49" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="N49" t="n">
-        <v>4.75</v>
+        <v>1.62</v>
       </c>
       <c r="O49" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="P49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="R49" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S49" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T49" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="U49" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="V49" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W49" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AI49" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1.2</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4.1</v>
+        <v>2.38</v>
       </c>
       <c r="M50" t="n">
-        <v>3.88</v>
+        <v>3.33</v>
       </c>
       <c r="N50" t="n">
-        <v>1.62</v>
+        <v>2.87</v>
       </c>
       <c r="O50" t="n">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="P50" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="R50" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S50" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="T50" t="n">
-        <v>2.63</v>
+        <v>3.18</v>
       </c>
       <c r="U50" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="V50" t="n">
-        <v>6.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W50" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X50" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.95</v>
+        <v>2.94</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD50" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AG50" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AH50" t="n">
-        <v>5.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,76 +7274,76 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>16.25</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,76 +7670,76 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -7766,22 +7766,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,76 +7934,76 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.27</v>
+        <v>1.51</v>
       </c>
       <c r="M57" t="n">
-        <v>3.38</v>
+        <v>4.4</v>
       </c>
       <c r="N57" t="n">
-        <v>1.93</v>
+        <v>5.7</v>
       </c>
       <c r="O57" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="P57" t="n">
-        <v>14.75</v>
+        <v>16.25</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="R57" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S57" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="T57" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="U57" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V57" t="n">
-        <v>6</v>
+        <v>5.65</v>
       </c>
       <c r="W57" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X57" t="n">
         <v>1.01</v>
       </c>
       <c r="Y57" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.96</v>
+        <v>4.3</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.79</v>
+        <v>2.19</v>
       </c>
       <c r="AD57" t="n">
-        <v>2.79</v>
+        <v>2.53</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG57" t="n">
         <v>2</v>
       </c>
       <c r="AH57" t="n">
-        <v>5.45</v>
+        <v>4.65</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.99</v>
+        <v>1.61</v>
       </c>
       <c r="M63" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="N63" t="n">
-        <v>2.92</v>
+        <v>5.2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,16 +8774,16 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AC63" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M64" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="N64" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8876,58 +8876,58 @@
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.62</v>
+        <v>1.99</v>
       </c>
       <c r="M65" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="N65" t="n">
-        <v>6.2</v>
+        <v>2.92</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9008,58 +9008,58 @@
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA65" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>2.47</v>
-      </c>
       <c r="AC65" t="n">
-        <v>1.43</v>
+        <v>2.35</v>
       </c>
       <c r="AD65" t="n">
-        <v>5.05</v>
+        <v>2.55</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.1</v>
+        <v>1.49</v>
       </c>
       <c r="AF65" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,22 +9350,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="M68" t="n">
-        <v>3.15</v>
+        <v>3.61</v>
       </c>
       <c r="N68" t="n">
-        <v>2.67</v>
+        <v>3.91</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC72" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.51</v>
+        <v>2.53</v>
       </c>
       <c r="M73" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="N73" t="n">
-        <v>5.2</v>
+        <v>2.38</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>5.1</v>
+        <v>1.51</v>
       </c>
       <c r="M75" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="N75" t="n">
-        <v>1.61</v>
+        <v>5.2</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="M76" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="N76" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10583,43 +10583,43 @@
         <v>4.8</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB77" t="n">
         <v>1.8</v>
@@ -10628,22 +10628,22 @@
         <v>1.9</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AI77" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,76 +10706,76 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="M78" t="n">
-        <v>3.2</v>
+        <v>3.97</v>
       </c>
       <c r="N78" t="n">
-        <v>2.6</v>
+        <v>1.61</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC78" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AI78" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11252,58 +11252,58 @@
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11362,17 +11362,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>3.05</v>
+        <v>2.22</v>
       </c>
       <c r="M83" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="N83" t="n">
-        <v>2.31</v>
+        <v>3.5</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11384,58 +11384,58 @@
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11494,17 +11494,17 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11540,10 +11540,10 @@
         <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.59</v>
+        <v>4.08</v>
       </c>
       <c r="M85" t="n">
-        <v>3.18</v>
+        <v>2.82</v>
       </c>
       <c r="N85" t="n">
-        <v>2.39</v>
+        <v>2.02</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11648,58 +11648,58 @@
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.85</v>
+        <v>3.06</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI85" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.35</v>
+        <v>3.52</v>
       </c>
       <c r="M88" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="N88" t="n">
-        <v>7.2</v>
+        <v>1.86</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,16 +12074,16 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,76 +12158,76 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.52</v>
+        <v>1.35</v>
       </c>
       <c r="M89" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N89" t="n">
-        <v>1.86</v>
+        <v>7.2</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.82</v>
+        <v>1.3</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.88</v>
+        <v>3.4</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AI89" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.26</v>
+        <v>2.8</v>
       </c>
       <c r="M91" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="N91" t="n">
-        <v>2.16</v>
+        <v>3.18</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12440,58 +12440,58 @@
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI91" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,76 +12554,76 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.55</v>
+        <v>3.38</v>
       </c>
       <c r="M92" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N92" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S92" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T92" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V92" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W92" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X92" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB92" t="n">
         <v>2.6</v>
       </c>
-      <c r="N92" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" t="n">
-        <v>0</v>
-      </c>
-      <c r="W92" t="n">
-        <v>0</v>
-      </c>
-      <c r="X92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB92" t="n">
-        <v>0</v>
-      </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI92" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
@@ -12695,37 +12695,37 @@
         <v>2.58</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Z93" t="n">
         <v>1.55</v>
@@ -12734,28 +12734,28 @@
         <v>2.45</v>
       </c>
       <c r="AB93" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AI93" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="M94" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="N94" t="n">
-        <v>4.1</v>
+        <v>4.42</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12836,58 +12836,58 @@
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V94" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI94" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="M95" t="n">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="N95" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12992,16 +12992,16 @@
         <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13100,58 +13100,58 @@
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V96" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG96" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH96" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AI96" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13256,16 +13256,16 @@
         <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13388,10 +13388,10 @@
         <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13574,22 +13574,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.99</v>
+        <v>1.97</v>
       </c>
       <c r="M100" t="n">
-        <v>3.38</v>
+        <v>2.69</v>
       </c>
       <c r="N100" t="n">
-        <v>2.04</v>
+        <v>4.5</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13628,58 +13628,58 @@
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V100" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI100" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.74</v>
+        <v>1.36</v>
       </c>
       <c r="M101" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N101" t="n">
-        <v>2.37</v>
+        <v>7.3</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13784,16 +13784,16 @@
         <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB101" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.46</v>
+        <v>2.99</v>
       </c>
       <c r="M102" t="n">
-        <v>3.85</v>
+        <v>3.38</v>
       </c>
       <c r="N102" t="n">
-        <v>7</v>
+        <v>2.04</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="M104" t="n">
-        <v>4</v>
+        <v>3.03</v>
       </c>
       <c r="N104" t="n">
-        <v>7.3</v>
+        <v>3.08</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14180,16 +14180,16 @@
         <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AA104" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="M105" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="N105" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14324,10 +14324,10 @@
         <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AF105" t="n">
         <v>0</v>
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         <v>0</v>
       </c>
       <c r="AD106" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
         <v>0</v>
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14588,10 +14588,10 @@
         <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF107" t="n">
         <v>0</v>
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="M108" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N108" t="n">
-        <v>1.95</v>
+        <v>4</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14720,10 +14720,10 @@
         <v>0</v>
       </c>
       <c r="AD108" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AF108" t="n">
         <v>0</v>
@@ -14798,13 +14798,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="M109" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="N109" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14816,58 +14816,58 @@
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U109" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD109" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG109" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH109" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.69</v>
+        <v>2.31</v>
       </c>
       <c r="M110" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="N110" t="n">
-        <v>4.84</v>
+        <v>3.1</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14978,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD110" t="n">
         <v>0</v>
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.31</v>
+        <v>1.69</v>
       </c>
       <c r="M112" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="N112" t="n">
-        <v>3.1</v>
+        <v>4.84</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15242,10 +15242,10 @@
         <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="M113" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="N113" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,10 +15374,10 @@
         <v>1.95</v>
       </c>
       <c r="AB113" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="M114" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="N114" t="n">
-        <v>5.1</v>
+        <v>3.05</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="M115" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="N115" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC115" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G121" t="n">
